--- a/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
@@ -575,46 +575,46 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.73733091056275</v>
+        <v>16.6832298282651</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-15.64727461245261</v>
+        <v>-15.59785978178129</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6539378666742337</v>
+        <v>-0.6525658918177797</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5236382679579421</v>
+        <v>-0.5229249711847714</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.06265511454189</v>
+        <v>-1.060184339552215</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.765119857548676</v>
+        <v>-0.763385867676476</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8502228494618791</v>
+        <v>-0.8479777628399674</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.318527077831945</v>
+        <v>-1.314521177208327</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.380150625019368</v>
+        <v>-1.375632012841685</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.47676159304438</v>
+        <v>5.459501888293673</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.438499099651629</v>
+        <v>-2.430373255037757</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.11761296091595</v>
+        <v>-10.08518389836041</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.888131483447467</v>
+        <v>4.873025814205455</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.139913691221409</v>
+        <v>5.123909121036938</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14.17322834646427</v>
+        <v>14.12705497281897</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.105998582130546</v>
+        <v>-4.093172145713623</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.17286933519324</v>
+        <v>12.13332783124881</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.372626492561359</v>
+        <v>-4.359630889144618</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.77045107536068</v>
+        <v>11.7319933998663</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.616001821810457</v>
+        <v>-4.601974724860888</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702052933214894</v>
+        <v>-4.687509331806439</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.52403653085408</v>
+        <v>11.48709096772213</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.233883045990275</v>
+        <v>-5.217049249740114</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10.61637372510533</v>
+        <v>10.58263723700954</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.294143794709612</v>
+        <v>-6.273679846521233</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.261177044690541</v>
+        <v>-6.240899519496537</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.03154788207954</v>
+        <v>9.999963336543409</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.435400607744668</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.597470770697051</v>
+        <v>6.575277657116253</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.533723577793495</v>
+        <v>9.502889207930053</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.23650959593922</v>
+        <v>18.17724579110801</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.82263896899158</v>
+        <v>13.77736302686032</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.912598732583454</v>
+        <v>-4.897811198957214</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.06497014896154951</v>
+        <v>-0.06544358322878452</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.954481257576333</v>
+        <v>8.925321991067307</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.171327526134199</v>
+        <v>-5.154977935802073</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.429378204676375</v>
+        <v>8.402503377692142</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.531652674115143</v>
+        <v>-1.526657427312436</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.819141830691102</v>
+        <v>2.81051628404429</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.412178075744457</v>
+        <v>7.388738392492996</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>16.11035330218589</v>
+        <v>16.05905278385278</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.36485994035601</v>
+        <v>16.31272030984813</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.12647710014824</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.90019268402924</v>
+        <v>20.83253266037659</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.17297924297438</v>
+        <v>12.13272333846774</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.30644975881044</v>
+        <v>12.26567049515013</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20.11213381625274</v>
+        <v>20.04654056616127</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>12.07125987405186</v>
+        <v>12.03173989509958</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20.33512862352939</v>
+        <v>20.26911218532963</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.176392026843558</v>
+        <v>3.16602435211535</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.115968050824314</v>
+        <v>3.105960481420745</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.61658656233833</v>
+        <v>10.58254264267869</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>18.7677555629778</v>
+        <v>18.70775034617292</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18.80699913954481</v>
+        <v>18.74670481064283</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>18.39024929526796</v>
+        <v>18.33118266321649</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>18.64536233770619</v>
+        <v>18.58544758257918</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>35</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.792275965504309</v>
+        <v>1.785154043303933</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1807959413547593</v>
+        <v>0.1795792867830599</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.072654733713783</v>
+        <v>-3.063908837370931</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.802239102383609</v>
+        <v>-5.784731713573628</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-9.202614521893267</v>
+        <v>-9.173847101575952</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.76783984635186</v>
+        <v>-11.73046245701663</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-14.71701336424513</v>
+        <v>-14.67005549559563</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.464678835865321</v>
+        <v>-9.434146200936006</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-18.11683789448561</v>
+        <v>-18.05805961228135</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-18.97342424967097</v>
+        <v>-18.91184408637368</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.59070339828178</v>
+        <v>-10.55614053687653</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.828731773610954</v>
+        <v>-4.81303242592557</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.345823302055905</v>
+        <v>3.334884829319051</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.59723210817603</v>
+        <v>3.585447582574098</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>23</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-13.36300353760128</v>
+        <v>-13.32076428429314</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.97828814521669</v>
+        <v>-14.93004521475952</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.023052102815008</v>
+        <v>2.015293623839135</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.154005276222946</v>
+        <v>2.14579944676322</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.736622497678013</v>
+        <v>-2.7285403361929</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.792859820075996</v>
+        <v>-6.771175840673834</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-15.58820654676921</v>
+        <v>-15.53772142033562</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-20.415841593133</v>
+        <v>-20.34912115788521</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11.76921145148025</v>
+        <v>-11.73029508326145</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.266622118964882</v>
+        <v>-8.239090858060862</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.115205382468375</v>
+        <v>-4.10127441366761</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2783468972936447</v>
+        <v>0.2776060088400882</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1428010783181932</v>
+        <v>-0.1425124143444449</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.469816935217871</v>
+        <v>4.455012799968685</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>20</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.493438320209975</v>
+        <v>-7.469994943745064</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8952422393719601</v>
+        <v>0.8919379962237102</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.501967046037066</v>
+        <v>-4.488405405317849</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.372654003280722</v>
+        <v>-4.359539186774263</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.10239636453747</v>
+        <v>10.06844983253671</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3900251651771427</v>
+        <v>0.3883820959595425</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3051684901147169</v>
+        <v>0.3040656743196237</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1630668447884958</v>
+        <v>-0.1620585198153961</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.234540810026964</v>
+        <v>-5.216638147208094</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.93479361367001</v>
+        <v>3.922598768014197</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>13.75586009061722</v>
+        <v>13.71131898788094</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>8.7802129861183</v>
+        <v>8.751575020357365</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.37639314297713</v>
+        <v>13.33233734257329</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>18.64691810516706</v>
+        <v>18.58544758257312</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>30</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8360917166898645</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7718450676863</v>
+        <v>-0.769680985679436</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.501993583890417</v>
+        <v>-4.488259447109272</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.634941079466202</v>
+        <v>5.615143870738756</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.912741773839471</v>
+        <v>-4.897489356129938</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.616331352771461</v>
+        <v>-4.601447475316313</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.974388110584471</v>
+        <v>1.967753894879912</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11.52439440146082</v>
+        <v>11.4867842214906</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>21.48633795400567</v>
+        <v>21.4161459586003</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>17.29881556302698</v>
+        <v>17.24229271644823</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.41446654469165</v>
+        <v>10.38040371832808</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>13.7945453691481</v>
+        <v>13.74896913253322</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.37691172105361</v>
+        <v>13.33229412773851</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>16.97550829040028</v>
+        <v>16.91878091590722</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>34</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.434614790798875</v>
+        <v>-5.417560119425353</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.719756742436715</v>
+        <v>4.703646312444953</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.444714211874064</v>
+        <v>-7.420943052028534</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.457639633372743</v>
+        <v>4.441442808700401</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.75236271849472</v>
+        <v>12.70896671259143</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.163386639763196</v>
+        <v>7.139239030746303</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.97175389125018</v>
+        <v>12.92834349063782</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.667483802233654</v>
+        <v>3.655452690297281</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6600016057815452</v>
+        <v>0.6580963723204363</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.704066453906989</v>
+        <v>5.685274891307373</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.551592999380468</v>
+        <v>2.54318735054747</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.536586614981672</v>
+        <v>5.517795857892104</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.067128125541878</v>
+        <v>8.039481976380479</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>11.27114551074455</v>
+        <v>11.23250640610749</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.775489602260677</v>
+        <v>-3.856440853566056</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.823652201444041</v>
+        <v>-2.885382166950478</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.042360890904824</v>
+        <v>7.211067911855821</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.042560314827725</v>
+        <v>2.100028285052822</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.062605764806676</v>
+        <v>-1.078469807948132</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.937024726178997</v>
+        <v>7.100732862133079</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8502571663772116</v>
+        <v>-0.8661833612173737</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.387471065221654</v>
+        <v>6.534543943104858</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.327879273088001</v>
+        <v>6.472279406413776</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.477539974873345</v>
+        <v>5.603772046803243</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.844462068470378</v>
+        <v>8.025668617759322</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.88142772192549</v>
+        <v>8.067117472003673</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.462412553471559</v>
+        <v>7.641847870274695</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6.581463054936599</v>
+        <v>6.743342319417501</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>12.50656167979002</v>
+        <v>12.46652153113075</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.395910372550532</v>
+        <v>3.384842703843056</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.004481252997159</v>
+        <v>7.97830989639499</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.133200370984078</v>
+        <v>3.121888858392204</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.595055699418644</v>
+        <v>2.585742434458496</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.893460204786635</v>
+        <v>2.883699430452701</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.313247746403903</v>
+        <v>5.29607125001187</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1627549867495759</v>
+        <v>-0.1623588390199942</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.291703854218532</v>
+        <v>7.268862392758002</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.947516985717968</v>
+        <v>8.919295709049649</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.238112684980884</v>
+        <v>6.218294707683491</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.260270690183368</v>
+        <v>1.255590876795083</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.668335665527586</v>
+        <v>-1.664273749700882</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.925345976013659</v>
+        <v>-3.914552417425746</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>58</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.4866746237239</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6.24151839309755</v>
+        <v>6.221085512327058</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6731110814921948</v>
+        <v>0.6696435125339946</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.529344217290195</v>
+        <v>2.519664216027458</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>8.894938457728799</v>
+        <v>8.86528726266156</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.468612411550581</v>
+        <v>7.444003582360828</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4781738214777249</v>
+        <v>0.4759727611441704</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.717377850488468</v>
+        <v>-1.712012458516874</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.506724700558458</v>
+        <v>-3.495716433302917</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.553461229413621</v>
+        <v>2.544900501380489</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6201612069294882</v>
+        <v>0.6177470722572878</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.074029205073316</v>
+        <v>-1.071384994795679</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.49547629968675</v>
+        <v>-1.491859956597445</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.974317702849191</v>
+        <v>-2.966276555356416</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>76</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.71708799557949</v>
+        <v>6.694112142292283</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9.055410844768105</v>
+        <v>9.025074351560569</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>8.662948269601472</v>
+        <v>8.633343234420046</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12.74645923897697</v>
+        <v>12.70316488599561</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>13.52827498942476</v>
+        <v>13.48246174918056</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>13.82970100063292</v>
+        <v>13.78348863205574</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.74845377519156</v>
+        <v>13.70297048438362</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>9.328894445681563</v>
+        <v>9.298493070146073</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>11.90758856235505</v>
+        <v>11.86881477553026</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5069554595466101</v>
+        <v>0.5047460423334797</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.621135070694173</v>
+        <v>1.615374441065661</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.656353913690928</v>
+        <v>1.650205320590345</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.08448060870939145</v>
+        <v>-0.08532638127984171</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.153801192601115</v>
+        <v>-1.15139452268717</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-18.24686297774453</v>
+        <v>-18.69663002478296</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-11.64235490351435</v>
+        <v>-11.92565324023172</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-9.299206599473663</v>
+        <v>-9.519037266910154</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.05807278569732</v>
+        <v>-5.165234573778193</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.226873315567062</v>
+        <v>-4.312787494354822</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-12.16077211930204</v>
+        <v>-12.45206299626057</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.504797511877243</v>
+        <v>-9.732561028457454</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.485892335283722</v>
+        <v>-4.594376078487237</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.666822514264247</v>
+        <v>-8.880014752697399</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.89484606083446</v>
+        <v>-11.16603668841495</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.98214732358668</v>
+        <v>-7.154277788446002</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-11.67321037201114</v>
+        <v>-11.9619457460182</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-18.18446839803945</v>
+        <v>-18.63610473561639</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-16.56847660689724</v>
+        <v>-16.97793269911506</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.410671268831436</v>
+        <v>6.484620027887964</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.800518435916665</v>
+        <v>4.85740883708344</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.889518490630365</v>
+        <v>10.00638983624751</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.02305606439044</v>
+        <v>10.14480846073801</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.744272656525716</v>
+        <v>6.829218673106318</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.671978022573967</v>
+        <v>5.740947425779233</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.472095477503252</v>
+        <v>1.492466125860084</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.376650419031748</v>
+        <v>2.404838289488701</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.689098777417733</v>
+        <v>3.731707991493373</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.09088766132422421</v>
+        <v>0.09156868760729253</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.088647604577503</v>
+        <v>-2.111735629434754</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.547993247149272</v>
+        <v>-7.632908027645193</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.962970595269063</v>
+        <v>-8.053162638589782</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.223556017000902</v>
+        <v>-2.247885750757305</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>92</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.667351363688233</v>
+        <v>-4.65585195442123</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.193378146985097</v>
+        <v>-5.180690918341703</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.677286366181377</v>
+        <v>-6.661569292984559</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-11.98791579005581</v>
+        <v>-11.95913789789984</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-10.35377481428771</v>
+        <v>-10.32915197673569</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.705036966529065</v>
+        <v>-5.691584378042236</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-12.32484626576532</v>
+        <v>-12.29363109806625</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.529357561730805</v>
+        <v>-9.504919252044473</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.68273135540166</v>
+        <v>-10.65525327545771</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.5386266447354</v>
+        <v>-11.50843158047974</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-12.83362579597009</v>
+        <v>-12.80014142653645</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-14.97906724746905</v>
+        <v>-14.93967131266903</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-15.40058183228064</v>
+        <v>-15.35992592361418</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-15.14967464224789</v>
+        <v>-15.11020459133814</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>97</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.238520442676858</v>
+        <v>5.224063582799211</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.528087755734099</v>
+        <v>-1.524529064037338</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.049587432549266</v>
+        <v>-6.034669751643861</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-11.07997926554753</v>
+        <v>-11.05201677389959</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.300555418773598</v>
+        <v>-1.298858650532878</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.003239029901067</v>
+        <v>-1.001655627389717</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.088958931623061</v>
+        <v>-1.086160152856721</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.623875639256013</v>
+        <v>-3.613919721921718</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4473481146033293</v>
+        <v>0.4464832049555696</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.439247248190242</v>
+        <v>-1.434473714051883</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.490267761766901</v>
+        <v>2.484484301836957</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.524259381135273</v>
+        <v>2.518867459182161</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.03526529734799766</v>
+        <v>0.03675717813415957</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2862395511503451</v>
+        <v>0.286478510410447</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>98</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-10.65670362633289</v>
+        <v>-10.62805014838577</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-11.2512771804744</v>
+        <v>-11.22060424048281</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-16.7548741513839</v>
+        <v>-16.7094441654531</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-16.62952296245049</v>
+        <v>-16.58453047414024</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-13.08660588354438</v>
+        <v>-13.05219920937466</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-12.79292574236054</v>
+        <v>-12.75862916926818</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-13.9046295516214</v>
+        <v>-13.86620618095829</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-11.30971941083438</v>
+        <v>-11.27790244283163</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-8.305458883381299</v>
+        <v>-8.282159450698231</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.138058426600594</v>
+        <v>-8.114465298314684</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.319821659782953</v>
+        <v>-7.298810459366493</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.262614440785839</v>
+        <v>-6.244019138756222</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.70768546717143</v>
+        <v>-7.684681912965964</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-12.57283157582705</v>
+        <v>-12.5370013970162</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>101</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.008289805358267</v>
+        <v>-1.005376708844153</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3504911019549937</v>
+        <v>0.3499736867805012</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.998203258428155</v>
+        <v>-4.983474246747605</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.833597427618407</v>
+        <v>-8.808024299916966</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-10.36639853599926</v>
+        <v>-10.33758670255492</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.07209189025944</v>
+        <v>-10.04339889794817</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.15297896034733</v>
+        <v>-11.11998661904961</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.61747965566376</v>
+        <v>-12.57991985173587</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-16.65286687632436</v>
+        <v>-16.60426184115414</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-18.50456907292661</v>
+        <v>-18.44988659554599</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-18.7094989389341</v>
+        <v>-18.65463991986402</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-17.68253470040873</v>
+        <v>-17.63015775261737</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-15.12575223457299</v>
+        <v>-15.0801153338593</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-17.85386241668046</v>
+        <v>-17.80069103128599</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>114</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.370631302666311</v>
+        <v>-3.360513667236319</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.983899245290417</v>
+        <v>-4.968650278350644</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.747517738666616</v>
+        <v>-2.738413951530916</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.862111448591719</v>
+        <v>-0.8583438348320556</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.279533648791478</v>
+        <v>-2.272639932461914</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.618700153394457</v>
+        <v>-4.604132089419494</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.585088470386339</v>
+        <v>-5.566255991179304</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.814316255924602</v>
+        <v>-7.788327588518612</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.119240517930692</v>
+        <v>-6.098401300622122</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.97523896805636</v>
+        <v>-6.950841954239984</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.180181365084799</v>
+        <v>-7.155595278557563</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.26628245044612</v>
+        <v>-6.244019138755789</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.688144179432577</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.437666556313275</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.768800639050383</v>
+        <v>-1.777577623243985</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.931888033101508</v>
+        <v>-1.942233299936007</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.648638487954322</v>
+        <v>5.672180452633128</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.6046427636755</v>
+        <v>3.618869959395141</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.792648761688881</v>
+        <v>3.809184120776763</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.187709060401708</v>
+        <v>1.190893081688237</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.006510388273931</v>
+        <v>4.020054055197953</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.812170850035599</v>
+        <v>2.819063178615899</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.608024044467193</v>
+        <v>-1.62062335072681</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1372036661054352</v>
+        <v>0.1307305902599509</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.06725251919687025</v>
+        <v>-0.07402273405762827</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.03257222283650663</v>
+        <v>-0.03963957671219731</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4503011521521856</v>
+        <v>-0.4598941876572624</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.381695010129846</v>
+        <v>-2.39995387727862</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>188</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.557268107444017</v>
+        <v>-3.545992442320369</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.638808957539858</v>
+        <v>-4.623751911550421</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.97103657770765</v>
+        <v>-3.95875325149153</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9502322779616605</v>
+        <v>0.948336680748902</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1209351383054127</v>
+        <v>-0.1206942210590611</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.840609482787471</v>
+        <v>2.833557072116989</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.442921386400748</v>
+        <v>-0.439054675007462</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.6871777136567871</v>
+        <v>0.6887345314358413</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.692492977920722</v>
+        <v>1.691369830265366</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.506332549389988</v>
+        <v>3.500819113322542</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.368351833294625</v>
+        <v>4.359895576239012</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.268575960942194</v>
+        <v>2.266619159116352</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.380070818765844</v>
+        <v>2.378279441788585</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.563326449446592</v>
+        <v>1.564170986830717</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>195</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.185746012517555</v>
+        <v>-0.1834705845880293</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.311383981844678</v>
+        <v>-2.301433233507737</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.451196885991266</v>
+        <v>3.44175857781412</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.069615026157059</v>
+        <v>3.060694766362595</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.713536224040148</v>
+        <v>-6.692304810174541</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.904952590220425</v>
+        <v>-5.885281352381483</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.909690284461021</v>
+        <v>-2.897394847740237</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.894784960131744</v>
+        <v>-3.878427998292409</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.929227042019413</v>
+        <v>-2.915831479063726</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.239404913116985</v>
+        <v>-2.227495125629993</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.47306954135577</v>
+        <v>-3.457889475588594</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.410482592217022</v>
+        <v>-2.39786529260202</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.318168250209219</v>
+        <v>-2.305299390726532</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5247262059869939</v>
+        <v>-0.5171165199887042</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.514959724982646</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.678061649532793</v>
+        <v>-2.704202611531763</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.670297612596173</v>
+        <v>-5.711689362456283</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.59071701669405</v>
+        <v>-4.623123331846635</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.69733377527708</v>
+        <v>-3.726559005222242</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.612733876067651</v>
+        <v>-3.643322664960323</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.3097571973558</v>
+        <v>-1.327708019581408</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.680622784669794</v>
+        <v>-3.717883262431094</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.221214424913569</v>
+        <v>-4.261985325217346</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.154418089964224</v>
+        <v>-3.189033587168453</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.881185947273607</v>
+        <v>-2.913017680716806</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.232857062344031</v>
+        <v>-5.282480677217642</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8746402398601845</v>
+        <v>-0.8950429804701159</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.491171825650241</v>
+        <v>-3.529937032809215</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.284233299289667</v>
+        <v>-2.304672201192204</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.663558493538922</v>
+        <v>-3.696427490375534</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.9615860815708928</v>
+        <v>0.9626950570373367</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.840043386204748</v>
+        <v>-1.855016512803722</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.207368692134224</v>
+        <v>1.20959317887678</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.425476629797302</v>
+        <v>-1.442264608441718</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.858908909974708</v>
+        <v>-4.900116820835549</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.639864720174458</v>
+        <v>2.6431373133736</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7742174218259592</v>
+        <v>-0.7931440399204703</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.779737304540447</v>
+        <v>-0.7993873684083113</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.499535955027014</v>
+        <v>-3.535786262346242</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.462631376383875</v>
+        <v>-3.501403105000712</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.204601541658448</v>
+        <v>-2.233894002865348</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.889426607487934</v>
+        <v>-4.93775916847936</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.900927876973199</v>
+        <v>4.92281845243032</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.697804968234216</v>
+        <v>4.713965005292437</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.838147529243344</v>
+        <v>1.844511635317772</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.162428885376663</v>
+        <v>2.170944538171987</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.330447567549584</v>
+        <v>2.339425420276051</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.924856600531726</v>
+        <v>1.927622689349676</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.339318565876205</v>
+        <v>1.334029658918226</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.592470252640631</v>
+        <v>-1.614353039321145</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.005288094314473</v>
+        <v>-2.032034425053787</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.554684993462899</v>
+        <v>-3.59137946823774</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.347396455771303</v>
+        <v>-2.377693076243261</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.367952084694686</v>
+        <v>-3.407139706131872</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.140427359166033</v>
+        <v>-4.182004246154868</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.536187757615508</v>
+        <v>-3.577672984800571</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>299</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.9884215978019526</v>
+        <v>-0.986220928804606</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.415568538468825</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.657071275222329</v>
+        <v>-1.654030079940959</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.526818142614786</v>
+        <v>-1.524078920729515</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.065239357686998</v>
+        <v>-2.061669708962363</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9077878643095971</v>
+        <v>0.9084334713111915</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.157502307572479</v>
+        <v>1.159131852972749</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.6889907083145843</v>
+        <v>0.6916471092673717</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3788373404394605</v>
+        <v>-0.3740254589967478</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.574921908181381</v>
+        <v>-3.565287767770421</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.44500306927717</v>
+        <v>-3.435592931552812</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.751124884909075</v>
+        <v>-4.739002416347965</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.827236433229977</v>
+        <v>-2.818119903547</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.912868384209276</v>
+        <v>-2.902846731805873</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.439895013123362</v>
+        <v>2.442489342990406</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.571678599840901</v>
+        <v>-1.576910180473547</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.299880639770819</v>
+        <v>-3.3075920945411</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.102960840496714</v>
+        <v>-2.108306876858784</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.8252846110978069</v>
+        <v>0.8247647913266718</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5893932154801718</v>
+        <v>0.5878099112231041</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.304659498207897</v>
+        <v>1.302346538675671</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3406011692169102</v>
+        <v>-0.3466192345024623</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.465302447688387</v>
+        <v>1.460968191853738</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.486983188187232</v>
+        <v>2.482500760836452</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.282468212889228</v>
+        <v>2.277747436518872</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.720922274203787</v>
+        <v>4.718547706163797</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.100793161314087</v>
+        <v>5.100432132652024</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.61825583869355</v>
+        <v>5.617533144072731</v>
       </c>
     </row>
     <row r="34">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr"/>
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.2544</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2462473089740129</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.2456</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4068~4081</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4068</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.3003483912709868</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.2368</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4062~4075</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4062</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.3216591791056871</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.2281</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4040~4053</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4040</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3592167559366004</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.2193</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4028~4041</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4028</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4023717525287083</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.2105</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3993~4006</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3993</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.4215461584526139</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.2017</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3970~3983</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3970</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3468151718293555</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.193</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3950~3963</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3950</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.3107484388069963</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.1842</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3920~3933</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3920</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3195252767317172</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.1754</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3886~3899</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3886</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.274920751602636</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.1667</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3848~3860</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3848</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.2395523098472836</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.1579</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3808~3820</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3808</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3730194720424365</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.1491</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3750~3762</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3750</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.340328272363088</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.1403</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3674~3686</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3674</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.4858420098464364</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.1316</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3603~3613</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3603</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.1269838502404141</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.1228</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3531~3540</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3531</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.2617999021308819</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.114</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3439~3448</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3439</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.1442503851751695</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.1053</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3342~3351</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3342</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3000632083030865</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.09649</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3244~3253</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3244</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.01194132934428893</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.08772</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3143~3152</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3143</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.04463274577987164</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.07895</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3029~3038</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3029</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.1727894612251859</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.07017</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2892~2900</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2892</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.2651823694451991</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.0614</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2704~2712</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2704</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.5301604998490177</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.05263</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2509~2517</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2509</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.5856240556342769</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.04386</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2301~2307</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2301</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.8659028154640538</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.03509</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2064~2068</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2064</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.229965935109178</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.02632</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1782~1784</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1782</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.6455751327048205</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.01754</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1483~1485</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1483</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.9745751478034919</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.008772</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1109~1110</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1109</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.4795346527630002</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.2544</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>12.98275215598051</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.2456</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>97~97</t>
-        </is>
+      <c r="B7" t="n">
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>13.48594312308899</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.2368</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B8" t="n">
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>13.52597915551819</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.2281</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>125~125</t>
-        </is>
+      <c r="B9" t="n">
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>12.30656167979002</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.2193</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>137~137</t>
-        </is>
+      <c r="B10" t="n">
+        <v>137</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>12.47006532942505</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.2105</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>172~172</t>
-        </is>
+      <c r="B11" t="n">
+        <v>172</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>10.29725935420863</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.2017</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>195~195</t>
-        </is>
+      <c r="B12" t="n">
+        <v>195</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>7.506561679790025</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.193</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>215~215</t>
-        </is>
+      <c r="B13" t="n">
+        <v>215</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>6.111212842580727</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.1842</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>245~245</t>
-        </is>
+      <c r="B14" t="n">
+        <v>245</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>5.465745353259408</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.1754</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>279~279</t>
-        </is>
+      <c r="B15" t="n">
+        <v>279</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>4.137386052549886</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.1667</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>317~318</t>
-        </is>
+      <c r="B16" t="n">
+        <v>317</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>3.166939038280589</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.1579</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>357~358</t>
-        </is>
+      <c r="B17" t="n">
+        <v>357</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>4.210472294315167</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.1491</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>415~416</t>
-        </is>
+      <c r="B18" t="n">
+        <v>415</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>3.275792449020798</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.1403</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>491~492</t>
-        </is>
+      <c r="B19" t="n">
+        <v>491</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>3.807374687920102</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.1316</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>562~565</t>
-        </is>
+      <c r="B20" t="n">
+        <v>562</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.9578891134183394</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.1228</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>634~638</t>
-        </is>
+      <c r="B21" t="n">
+        <v>634</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.581796789507891</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.114</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>726~730</t>
-        </is>
+      <c r="B22" t="n">
+        <v>726</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.794232912666736</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.1053</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>823~827</t>
-        </is>
+      <c r="B23" t="n">
+        <v>823</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.315509684626775</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.09649</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>921~925</t>
-        </is>
+      <c r="B24" t="n">
+        <v>921</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.047102220330558</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.08772</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1022~1026</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1022</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.05679114672069119</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.07895</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1136~1140</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1136</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.3881751623152425</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.07017</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1273~1278</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1273</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.5372567865636597</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.0614</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1461~1466</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1461</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.9245433679589539</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.05263</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1656~1661</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1656</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.837809181137132</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.04386</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1864~1871</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1864</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.023636075421088</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.03509</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2101~2110</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2101</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.166424102200494</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.02632</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2383~2394</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2383</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.4466546944789798</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.01754</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2682~2693</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2682</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.5068063112979857</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.008772</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3056~3068</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3056</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.1466325835737265</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3417~3430</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3417</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.2776948799767425</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.6832298282651</v>
+        <v>16.69572473846325</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-15.59785978178129</v>
+        <v>-15.5849999125943</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6525658918177797</v>
+        <v>-0.6395947972073017</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5229249711847714</v>
+        <v>-0.5099783574274994</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.060184339552215</v>
+        <v>-1.047103420931805</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.763385867676476</v>
+        <v>-0.7503693272897678</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8479777628399674</v>
+        <v>-0.8349347159548799</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.314521177208327</v>
+        <v>-1.301360467789358</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.375632012841685</v>
+        <v>-1.362450295199203</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.459501888293673</v>
+        <v>5.472894828350206</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.430373255037757</v>
+        <v>-2.416926592036809</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.08518389836041</v>
+        <v>-10.07173960849578</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.873025814205455</v>
+        <v>4.886578727407276</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.123909121036938</v>
+        <v>5.113479485342282</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14.12705497281897</v>
+        <v>14.13954781041102</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.093172145713623</v>
+        <v>-4.080304221309291</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.13332783124881</v>
+        <v>12.14630725535748</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.359630889144618</v>
+        <v>-4.346686746792869</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.7319933998663</v>
+        <v>11.74508113753807</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.601974724860888</v>
+        <v>-4.58896016573842</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.687509331806439</v>
+        <v>-4.67446802034511</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.48709096772213</v>
+        <v>11.50025622740372</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.217049249740114</v>
+        <v>-5.203868775940073</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10.58263723700954</v>
+        <v>10.5960313666962</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.273679846521233</v>
+        <v>-6.260233933462224</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.240899519496537</v>
+        <v>-6.22745480713256</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.999963336543409</v>
+        <v>10.01351654700717</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053130329</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.575277657116253</v>
+        <v>6.587764376092366</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.502889207930053</v>
+        <v>9.515766786791517</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.17724579110801</v>
+        <v>18.19022914223842</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.77736302686032</v>
+        <v>13.79031799229549</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.897811198957214</v>
+        <v>-4.884732722486703</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.06544358322878452</v>
+        <v>-0.05242701622106694</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.925321991067307</v>
+        <v>8.938368943308483</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.154977935802073</v>
+        <v>-5.14181886311804</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.402503377692142</v>
+        <v>8.415687880045219</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.526657427312436</v>
+        <v>-1.513266319977255</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.81051628404429</v>
+        <v>2.823963778286029</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.388738392492996</v>
+        <v>7.402184715940706</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>16.05905278385278</v>
+        <v>16.07260634989039</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.31272030984813</v>
+        <v>16.30229067414998</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.12647710014824</v>
+        <v>14.13896959564904</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.83253266037659</v>
+        <v>20.84541838006416</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.13272333846774</v>
+        <v>12.14570250838023</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.26567049515013</v>
+        <v>12.27862440066982</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20.04654056616127</v>
+        <v>20.05963255156743</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>12.03173989509958</v>
+        <v>12.04476219246445</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20.26911218532963</v>
+        <v>20.28216389225857</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.16602435211535</v>
+        <v>3.179186295968741</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.105960481420745</v>
+        <v>3.119143255601948</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.58254264267869</v>
+        <v>10.5959366102631</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>18.70775034617292</v>
+        <v>18.72120069847178</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18.74670481064283</v>
+        <v>18.76015249036211</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>18.33118266321649</v>
+        <v>18.34473635656506</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>18.58544758257918</v>
+        <v>18.57501794687347</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>35</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.785154043303933</v>
+        <v>1.79763629931211</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1795792867830599</v>
+        <v>0.1924494137163464</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.063908837370931</v>
+        <v>-3.050940348423893</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.784731713573628</v>
+        <v>-5.771789302065862</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-9.173847101575952</v>
+        <v>-9.16077165654513</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.73046245701663</v>
+        <v>-11.71745222601964</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-14.67005549559563</v>
+        <v>-14.65701916383974</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.434146200936006</v>
+        <v>-9.42098920035847</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-18.05805961228135</v>
+        <v>-18.04488364141296</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-18.91184408637368</v>
+        <v>-18.8984576093688</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.55614053687653</v>
+        <v>-10.5426957261474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.81303242592557</v>
+        <v>-4.799587726177364</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.334884829319051</v>
+        <v>3.348437568282776</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.585447582574098</v>
+        <v>3.575017946878539</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>23</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-13.32076428429314</v>
+        <v>-13.3082950009593</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.93004521475952</v>
+        <v>-14.91718712814716</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.015293623839135</v>
+        <v>2.028265057028172</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.14579944676322</v>
+        <v>2.158746291581259</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.7285403361929</v>
+        <v>-2.715461808315901</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.771175840673834</v>
+        <v>-6.758163658709535</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-15.53772142033562</v>
+        <v>-15.52468600230472</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-20.34912115788521</v>
+        <v>-20.33596870711114</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11.73029508326145</v>
+        <v>-11.71711752319179</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.239090858060862</v>
+        <v>-8.225702017569951</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.10127441366761</v>
+        <v>-4.08782858704059</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2776060088400882</v>
+        <v>0.2910512344144678</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1425124143444449</v>
+        <v>-0.1289599411009519</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.455012799968685</v>
+        <v>4.444583164266575</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>20</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.469994943745064</v>
+        <v>-7.457521493757575</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8919379962237102</v>
+        <v>0.9048075281879733</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.488405405317849</v>
+        <v>-4.475438912842911</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.359539186774263</v>
+        <v>-4.34659683306586</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.06844983253671</v>
+        <v>10.08153535760646</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3883820959595425</v>
+        <v>0.4013975702701416</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3040656743196237</v>
+        <v>0.3171077755649279</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1620585198153961</v>
+        <v>-0.1488987148229768</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.216638147208094</v>
+        <v>-5.203458774326378</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.922598768014197</v>
+        <v>3.935990522049934</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>13.71131898788094</v>
+        <v>13.72476810244164</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>8.751575020357365</v>
+        <v>8.765021254819082</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.33233734257329</v>
+        <v>13.34589064007265</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>18.58544758257312</v>
+        <v>18.57501794687952</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>30</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8360917166898645</v>
+        <v>0.8485714718820105</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.769680985679436</v>
+        <v>-0.7568132491842903</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.488259447109272</v>
+        <v>-4.475293508528736</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.615143870738756</v>
+        <v>5.62809219684496</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.897489356129938</v>
+        <v>-4.884412819549333</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.601447475316313</v>
+        <v>-4.588434938534135</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.967753894879912</v>
+        <v>1.980796446940523</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11.4867842214906</v>
+        <v>11.49994829531995</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>21.4161459586003</v>
+        <v>21.42933371514734</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>17.24229271644823</v>
+        <v>17.25568777511856</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.38040371832808</v>
+        <v>10.39385211244165</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>13.74896913253322</v>
+        <v>13.76241595409726</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.33229412773851</v>
+        <v>13.34584740120901</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>16.91878091590722</v>
+        <v>16.90835128021057</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>34</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.417560119425353</v>
+        <v>-5.405086410429959</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.703646312444953</v>
+        <v>4.716517684772683</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.420943052028534</v>
+        <v>-7.407979968554805</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.441442808700401</v>
+        <v>4.454389918034749</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.70896671259143</v>
+        <v>12.72205310790343</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.139239030746303</v>
+        <v>7.152257235405756</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.92834349063782</v>
+        <v>12.94139073854005</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.655452690297281</v>
+        <v>3.668613453158422</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6580963723204363</v>
+        <v>0.6712772000356324</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.685274891307373</v>
+        <v>5.698666800650429</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.54318735054747</v>
+        <v>2.556634076163306</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.517795857892104</v>
+        <v>5.531241529864381</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.039481976380479</v>
+        <v>8.05303486843593</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>11.23250640610749</v>
+        <v>11.22207677040667</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.856440853566056</v>
+        <v>-3.751225967510443</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.885382166950478</v>
+        <v>-2.801797404394712</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.211067911855821</v>
+        <v>7.030763791377275</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.100028285052822</v>
+        <v>2.047135806520508</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.078469807948132</v>
+        <v>-1.047217647134865</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.100732862133079</v>
+        <v>6.926200486784559</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8661833612173737</v>
+        <v>-0.8348972259396348</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.534543943104858</v>
+        <v>6.379213346674497</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.472279406413776</v>
+        <v>6.320031698280111</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.603772046803243</v>
+        <v>5.47254756710155</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>8.025668617759322</v>
+        <v>7.831519330869682</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>8.067117472003673</v>
+        <v>7.867830338614574</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.641847870274695</v>
+        <v>7.449832971456416</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6.743342319417501</v>
+        <v>7.677582049442513</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>12.46652153113075</v>
+        <v>12.47567244869149</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.384842703843056</v>
+        <v>3.396789176623031</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.97830989639499</v>
+        <v>7.989101928763404</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.121888858392204</v>
+        <v>3.133891249911805</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.585742434458496</v>
+        <v>2.598045622812087</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.883699430452701</v>
+        <v>2.895901059537721</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.29607125001187</v>
+        <v>5.30768279626097</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1623588390199942</v>
+        <v>-0.1491673709983914</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.268862392758002</v>
+        <v>7.280141371226222</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.919295709049649</v>
+        <v>8.93033626633499</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.218294707683491</v>
+        <v>6.230090313724745</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.255590876795083</v>
+        <v>1.268645748389062</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.664273749700882</v>
+        <v>-1.650383138640542</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.914552417425746</v>
+        <v>-3.924982053123898</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>58</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.4866746237239</v>
+        <v>-2.473637763647652</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6.221085512327058</v>
+        <v>6.232252971330524</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6696435125339946</v>
+        <v>0.6823211037118426</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.519664216027458</v>
+        <v>2.531801315803619</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>8.86528726266156</v>
+        <v>8.875898859847773</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.444003582360828</v>
+        <v>7.45496978080817</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4759727611441704</v>
+        <v>0.4888293265855523</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.712012458516874</v>
+        <v>-1.698408136771413</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.495716433302917</v>
+        <v>-3.481620825727745</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.544900501380489</v>
+        <v>2.557577357898388</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6177470722572878</v>
+        <v>0.630991573116674</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.071384994795679</v>
+        <v>-1.057720307371525</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.491859956597445</v>
+        <v>-1.478006569331157</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.966276555356416</v>
+        <v>-2.976706191054568</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>76</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.694112142292283</v>
+        <v>6.704677661351411</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9.025074351560569</v>
+        <v>9.035417756356161</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>8.633343234420046</v>
+        <v>8.643847729771991</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12.70316488599561</v>
+        <v>12.71250710673305</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>13.48246174918056</v>
+        <v>13.49172877176881</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>13.78348863205574</v>
+        <v>13.79265750226909</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.70297048438362</v>
+        <v>13.71222610007329</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>9.298493070146073</v>
+        <v>9.30912082078688</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>11.86881477553026</v>
+        <v>11.87876677049054</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5047460423334797</v>
+        <v>0.5179510571245132</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.615374441065661</v>
+        <v>1.62833987159123</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.650205320590345</v>
+        <v>1.663137383181699</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.08532638127984171</v>
+        <v>-0.07184488242017295</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.15139452268717</v>
+        <v>-1.161824158385322</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>71</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-18.69663002478296</v>
+        <v>-18.67871557915954</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-11.92565324023172</v>
+        <v>-11.90920004330991</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-9.519037266910154</v>
+        <v>-9.503191478653534</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.165234573778193</v>
+        <v>-5.150677546556061</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.312787494354822</v>
+        <v>-4.298328778903759</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-12.45206299626057</v>
+        <v>-12.43536439070593</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.732561028457454</v>
+        <v>-9.716545109078886</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.594376078487237</v>
+        <v>-4.579573641141877</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.880014752697399</v>
+        <v>-8.864014070409958</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-11.16603668841495</v>
+        <v>-11.14916633041026</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.154277788446002</v>
+        <v>-7.138461310117002</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-11.9619457460182</v>
+        <v>-12.73641368293776</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-18.63610473561639</v>
+        <v>-19.41549685444577</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-16.97793269911506</v>
+        <v>-16.98836233481321</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>72</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.484620027887964</v>
+        <v>6.495434920073983</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.85740883708344</v>
+        <v>4.86905046516533</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.00638983624751</v>
+        <v>10.01661793555967</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.14480846073801</v>
+        <v>10.15488730782896</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.829218673106318</v>
+        <v>6.840364730230753</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.740947425779233</v>
+        <v>5.752433429211067</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.492466125860084</v>
+        <v>1.505209156771805</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.404838289488701</v>
+        <v>2.417504989921383</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.731707991493373</v>
+        <v>3.744032061726216</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.09156868760729253</v>
+        <v>0.1051682601932455</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.111735629434754</v>
+        <v>-2.879046617879858</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.632908027645193</v>
+        <v>-7.619455738925083</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.053162638589782</v>
+        <v>-8.039606592238179</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.247885750757305</v>
+        <v>-2.258315386455457</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>92</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.65585195442123</v>
+        <v>-4.642098424756831</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.180690918341703</v>
+        <v>-5.166414745100596</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.661569292984559</v>
+        <v>-6.646855183728206</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-11.95913789789984</v>
+        <v>-11.94299837073645</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-10.32915197673569</v>
+        <v>-10.3133366504825</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.691584378042236</v>
+        <v>-5.677071115294318</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-12.29363109806625</v>
+        <v>-12.27711837659692</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.504919252044473</v>
+        <v>-9.489038805221924</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.65525327545771</v>
+        <v>-10.63901225048783</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.50843158047974</v>
+        <v>-11.49167703848792</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-12.80014142653645</v>
+        <v>-12.78668413282623</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-14.93967131266903</v>
+        <v>-14.92621902394892</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-15.35992592361418</v>
+        <v>-15.34636987726258</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-15.11020459133814</v>
+        <v>-15.12063422703629</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.224063582799211</v>
+        <v>5.664953705763551</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.524529064037338</v>
+        <v>-1.028660983731463</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.034669751643861</v>
+        <v>-5.495315391333563</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-11.05201677389959</v>
+        <v>-10.45859102131219</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.298858650532878</v>
+        <v>-0.8130509241658501</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.001655627389717</v>
+        <v>-0.5157824724387794</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.086160152856721</v>
+        <v>-0.5999827541244045</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.613919721921718</v>
+        <v>-3.105665887658034</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4464832049555696</v>
+        <v>0.9116514837666827</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.434473714051883</v>
+        <v>-0.9578160415621682</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.484484301836957</v>
+        <v>2.918728466996789</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.518867459182161</v>
+        <v>2.953106619351878</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.03675717813415957</v>
+        <v>0.4921394395083212</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.286478510410447</v>
+        <v>0.7178750897346191</v>
       </c>
     </row>
     <row r="23">
@@ -1456,205 +1456,205 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-10.62805014838577</v>
+        <v>-11.21022420231525</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-11.22060424048281</v>
+        <v>-11.79185010913614</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-16.7094441654531</v>
+        <v>-17.33159651219797</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-16.58453047414024</v>
+        <v>-17.20694552409515</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-13.05219920937466</v>
+        <v>-13.63384195610912</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-12.75862916926818</v>
+        <v>-13.34052591396243</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-13.86620618095829</v>
+        <v>-14.45830229639236</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-11.27790244283163</v>
+        <v>-11.83926448979268</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-8.282159450698231</v>
+        <v>-8.813077800379006</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.114465298314684</v>
+        <v>-8.63478666964091</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.298810459366493</v>
+        <v>-7.811336754968288</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.244019138756222</v>
+        <v>-6.746030767561891</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.684681912965964</v>
+        <v>-8.197109455926842</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-12.5370013970162</v>
+        <v>-13.1260129809578</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.09211</t>
+          <t>X ≈ -0.09209</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>101</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.005376708844153</v>
+        <v>-0.9925829438703246</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3499736867805012</v>
+        <v>0.3627785305225899</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.983474246747605</v>
+        <v>-4.968877387310833</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.808024299916966</v>
+        <v>-8.792247261474522</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-10.33758670255492</v>
+        <v>-10.32131271206872</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.04339889794817</v>
+        <v>-10.02719964078543</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.11998661904961</v>
+        <v>-11.10328076980732</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.57991985173587</v>
+        <v>-12.56258586852743</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-16.60426184115414</v>
+        <v>-16.58567686848735</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-18.44988659554599</v>
+        <v>-18.43041312914053</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-18.65463991986402</v>
+        <v>-18.64118262615381</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-17.63015775261737</v>
+        <v>-17.61670546389726</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-15.0801153338593</v>
+        <v>-15.0665592875077</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-17.80069103128599</v>
+        <v>-17.81112066698414</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.08334</t>
+          <t>X ≈ -0.08332</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>114</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.360513667236319</v>
+        <v>-3.34692572518157</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.968650278350644</v>
+        <v>-4.954102163933932</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.738413951530916</v>
+        <v>-2.724443785795394</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8583438348320556</v>
+        <v>-0.8449871299912033</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.272639932461914</v>
+        <v>-2.258799174843681</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.604132089419494</v>
+        <v>-4.589501932198068</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.566255991179304</v>
+        <v>-5.551123243722841</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.788327588518612</v>
+        <v>-7.772279457180346</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.098401300622122</v>
+        <v>-6.082900399316209</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.950841954239984</v>
+        <v>-6.934732960378859</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.155595278557563</v>
+        <v>-7.142137984847345</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.244019138755789</v>
+        <v>-6.230566850035679</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.07456</t>
+          <t>X ≈ -0.07455</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.777577623243985</v>
+        <v>-1.764310684842194</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.942233299936007</v>
+        <v>-1.928449741248301</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.672180452633128</v>
+        <v>5.683471094724808</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.618869959395141</v>
+        <v>3.630852339333714</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.809184120776763</v>
+        <v>3.821127433623175</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.190893081688237</v>
+        <v>1.203798945951405</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.020054055197953</v>
+        <v>4.032195618437051</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.819063178615899</v>
+        <v>2.831837902976474</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.62062335072681</v>
+        <v>-1.606327498363385</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1307305902599509</v>
+        <v>-0.2764756862935016</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.07402273405762827</v>
+        <v>-0.06056544034741052</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.03963957671219731</v>
+        <v>-0.02618728799208725</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4598941876572624</v>
+        <v>-0.4463381413056595</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.39995387727862</v>
+        <v>-2.410383512976772</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>188</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.545992442320369</v>
+        <v>-3.532125700893353</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.623751911550421</v>
+        <v>-4.609021031871535</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.95875325149153</v>
+        <v>-3.944263382560969</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.948336680748902</v>
+        <v>0.9610376256274478</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1206942210590611</v>
+        <v>-0.1075883149081349</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.833557072116989</v>
+        <v>2.845691635638048</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.439054675007462</v>
+        <v>-0.4255268876557992</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.6887345314358413</v>
+        <v>0.702095600890118</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.691369830265366</v>
+        <v>1.704421003231758</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.500819113322542</v>
+        <v>3.514224240975373</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.359895576239012</v>
+        <v>4.37335286994923</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.266619159116352</v>
+        <v>2.280071447836463</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.378279441788585</v>
+        <v>2.391835488140188</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.564170986830717</v>
+        <v>1.553741351132565</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1834705845880293</v>
+        <v>-0.1980241128462197</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.301433233507737</v>
+        <v>-2.550763272822238</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.44175857781412</v>
+        <v>3.158695650037068</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.060694766362595</v>
+        <v>2.780169849649894</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.692304810174541</v>
+        <v>-6.922035569372206</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.885281352381483</v>
+        <v>-6.117976995654558</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.897394847740237</v>
+        <v>-2.637165535846663</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.878427998292409</v>
+        <v>-3.614856074228399</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.915831479063726</v>
+        <v>-2.657735502609604</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.227495125629993</v>
+        <v>-1.978611191069781</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.457889475588594</v>
+        <v>-3.203720512595282</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.39786529260202</v>
+        <v>-2.14893419697465</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.305299390726532</v>
+        <v>-2.058880968655409</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5171165199887042</v>
+        <v>-0.302533073530924</v>
       </c>
     </row>
     <row r="29">
@@ -1768,153 +1768,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.514959724982646</v>
+        <v>-2.743366562042596</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.704202611531763</v>
+        <v>-2.442032476927444</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.711689362456283</v>
+        <v>-5.727490442518736</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.623123331846635</v>
+        <v>-4.368358496012831</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.726559005222242</v>
+        <v>-3.464823505229795</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.643322664960323</v>
+        <v>-3.65156923582574</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.327708019581408</v>
+        <v>-1.538565803774382</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.717883262431094</v>
+        <v>-3.936780440570949</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.261985325217346</v>
+        <v>-4.483050138844504</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.189033587168453</v>
+        <v>-3.403239013213131</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.913017680716806</v>
+        <v>-3.124848384033712</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.282480677217642</v>
+        <v>-5.505929168876456</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8950429804701159</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.529937032809215</v>
+        <v>-3.767977222204877</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.03948</t>
+          <t>X ≈ -0.03947</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>237</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.304672201192204</v>
+        <v>-2.292149911516582</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.696427490375534</v>
+        <v>-3.917116877410137</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.9626950570373367</v>
+        <v>0.9757021884549388</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.855016512803722</v>
+        <v>-1.840860060348945</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.20959317887678</v>
+        <v>0.9877850631062728</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.442264608441718</v>
+        <v>-1.429221712147353</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.900116820835549</v>
+        <v>-4.883993383747857</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.6431373133736</v>
+        <v>2.656048516801583</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7931440399204703</v>
+        <v>-0.7785355854803129</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7993873684083113</v>
+        <v>-0.7859822407554802</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.535786262346242</v>
+        <v>-3.522328968636025</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.501403105000712</v>
+        <v>-3.487950816280602</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.233894002865348</v>
+        <v>-2.220337956513745</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.93775916847936</v>
+        <v>-4.948188804177512</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.03071</t>
+          <t>X ≈ -0.0307</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>282</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.92281845243032</v>
+        <v>4.935340742105943</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.713965005292437</v>
+        <v>4.726874814868488</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.844511635317772</v>
+        <v>1.857518766735375</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.170944538171987</v>
+        <v>1.988897328399695</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.339425420276051</v>
+        <v>2.35253622465099</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.927622689349676</v>
+        <v>1.940665585644041</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.334029658918226</v>
+        <v>1.145539272002985</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.614353039321145</v>
+        <v>-1.599133841998913</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.032034425053787</v>
+        <v>-2.016320792418362</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.59137946823774</v>
+        <v>-3.577974340584909</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.377693076243261</v>
+        <v>-2.364235782533044</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.407139706131872</v>
+        <v>-3.393687417411762</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.182004246154868</v>
+        <v>-4.168448199803265</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.577672984800571</v>
+        <v>-3.588102620498724</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>299</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.986220928804606</v>
+        <v>-0.9736986391289832</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.415568538468825</v>
+        <v>2.428478348044877</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.654030079940959</v>
+        <v>-1.641022948523357</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.524078920729515</v>
+        <v>-1.511099778331051</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.061669708962363</v>
+        <v>-2.048558904587424</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9084334713111915</v>
+        <v>0.9214763676055568</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.159131852972749</v>
+        <v>1.172198107273225</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.6916471092673717</v>
+        <v>0.706110877023896</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3740254589967478</v>
+        <v>-0.358444478475711</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.565287767770421</v>
+        <v>-3.55188264011759</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.435592931552812</v>
+        <v>-3.422135637842594</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.739002416347965</v>
+        <v>-4.725550127627855</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.818119903547</v>
+        <v>-2.804563857195397</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.902846731805873</v>
+        <v>-2.913276367504025</v>
       </c>
     </row>
     <row r="33">
@@ -1979,52 +1979,52 @@
         <v>374</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.442489342990406</v>
+        <v>2.455011632666029</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.576910180473547</v>
+        <v>-1.564000370897496</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.3075920945411</v>
+        <v>-3.294584963123498</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.108306876858784</v>
+        <v>-2.095327734460319</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.8247647913266718</v>
+        <v>0.8378755957016111</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5878099112231041</v>
+        <v>0.6008528075174695</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.302346538675671</v>
+        <v>1.315412792976147</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3466192345024623</v>
+        <v>-0.4888997548993927</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.460968191853738</v>
+        <v>1.476340393026319</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.482500760836452</v>
+        <v>2.495905888489283</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.277747436518872</v>
+        <v>2.29120473022909</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.718547706163797</v>
+        <v>4.731999994883907</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.100432132652024</v>
+        <v>5.113988179003627</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.617533144072731</v>
+        <v>5.607103508374578</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.004386</t>
+          <t>X ≈ -0.004385</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2186,49 +2186,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2462473089740129</v>
+        <v>-0.2464837961021118</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1348189207139328</v>
+        <v>-0.1350918646826997</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2232432986173549</v>
+        <v>-0.2234970118958515</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2997179495979339</v>
+        <v>-0.2999523725849969</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2870218273699692</v>
+        <v>-0.2872625328691001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2207804211057933</v>
+        <v>-0.2210357708660524</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1454383491502256</v>
+        <v>-0.1457127410108257</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.06098242761055417</v>
+        <v>-0.0612802689691776</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03834601255881864</v>
+        <v>0.03802337402414935</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05854197068862277</v>
+        <v>0.0582094108861213</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1123910437614555</v>
+        <v>0.1120439816969281</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06261813775638814</v>
+        <v>0.06228329687890977</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1461133154632464</v>
+        <v>0.1457554781349231</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1157097732149452</v>
+        <v>0.1159292648586288</v>
       </c>
     </row>
     <row r="7">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3003483912709868</v>
+        <v>-0.3006122578738868</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08540409003698102</v>
+        <v>-0.08573113609512006</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2218713237619951</v>
+        <v>-0.2221676260002852</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2990046528229584</v>
+        <v>-0.2992813630487561</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2845510523802091</v>
+        <v>-0.2848349261979735</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2190464312322931</v>
+        <v>-0.2193446093439348</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1431932625283068</v>
+        <v>-0.1435107538704301</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05697652698499667</v>
+        <v>-0.05731835140106512</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0428646247343849</v>
+        <v>0.04249773079482821</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.04128226593718409</v>
+        <v>0.04091009645333088</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1205168883741408</v>
+        <v>0.1201237598877753</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.09504720031034708</v>
+        <v>0.09466036686414014</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.13100764621948</v>
+        <v>0.1306090779774962</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.09970520302771035</v>
+        <v>0.09996265073568367</v>
       </c>
     </row>
     <row r="8">
@@ -2290,101 +2290,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3216591791056871</v>
+        <v>-0.3219366389739946</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07948419630628933</v>
+        <v>-0.07983218494787536</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2401212486586175</v>
+        <v>-0.2404326639742322</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.293006682015978</v>
+        <v>-0.2933043922630176</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3023007487646083</v>
+        <v>-0.3026000003752856</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2125723864854336</v>
+        <v>-0.2128918174811787</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1364808311113492</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0740283253523657</v>
+        <v>-0.07438589938847429</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.05063406915753887</v>
+        <v>0.0502452570169396</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.02571157912614552</v>
+        <v>0.02532291269220366</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1299617875394219</v>
+        <v>0.1295458977563655</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1044060580944048</v>
+        <v>0.1039964955975847</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1164301636636154</v>
+        <v>0.1160145801152836</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1093274447122781</v>
+        <v>0.1095983062176344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.2281</t>
+          <t>X &gt; -0.228</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3592167559366004</v>
+        <v>-0.3595544123794454</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1316654376164834</v>
+        <v>-0.1320725159001768</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3404138414494255</v>
+        <v>-0.3407728173364362</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3696275071633224</v>
+        <v>-0.3699784067298069</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2772756918576249</v>
+        <v>-0.2776539672432747</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2133735829388002</v>
+        <v>-0.2137654194677481</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1858272821232205</v>
+        <v>-0.1862268166615948</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.04635978786971151</v>
+        <v>-0.04679779614617985</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.005153592724930434</v>
+        <v>0.004702139544370709</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03416507371566269</v>
+        <v>0.03369929554760631</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.115364708598058</v>
+        <v>0.1148769560657783</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.06473890181798225</v>
+        <v>0.06426372132202118</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.02961390187050483</v>
+        <v>0.02914375137610392</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.02109114693183045</v>
+        <v>0.02144209931476126</v>
       </c>
     </row>
     <row r="10">
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4023717525287083</v>
+        <v>-0.4027369112864605</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.194120844065317</v>
+        <v>-0.1945520122396118</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3775731379139273</v>
+        <v>-0.3779626172641102</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4072699043896719</v>
+        <v>-0.4076510882112601</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3378233073234256</v>
+        <v>-0.3382266746708567</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2498535635089283</v>
+        <v>-0.2502762984310607</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2467655327710432</v>
+        <v>-0.2471900056680525</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.05592994916062821</v>
+        <v>-0.0564060883043922</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.004084163646567163</v>
+        <v>-0.004573932283051363</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.002739917105046175</v>
+        <v>0.002240658720467081</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0599752777016036</v>
+        <v>0.0594597595135653</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.009082598216714644</v>
+        <v>0.008579763707608379</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02490914309875336</v>
+        <v>-0.0254075296520142</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.03421478088041852</v>
+        <v>-0.03381799256181495</v>
       </c>
     </row>
     <row r="11">
@@ -2446,49 +2446,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3993</v>
+        <v>3994</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4215461584526139</v>
+        <v>-0.4220191001625082</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.197396452525048</v>
+        <v>-0.1979433617409683</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3540264939166775</v>
+        <v>-0.3545389265804388</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.360134626823573</v>
+        <v>-0.360644368760866</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2603725603164477</v>
+        <v>-0.2609134362217844</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1492221306832917</v>
+        <v>-0.1497877762814426</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1203405017921142</v>
+        <v>-0.1209145874066593</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.02627329872620976</v>
+        <v>0.02565710872162441</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1541650576662974</v>
+        <v>0.1535159124389125</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1685326644433331</v>
+        <v>0.1678702128975047</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1530291353300157</v>
+        <v>0.1523679823473572</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.05135007275840309</v>
+        <v>0.05071443124540309</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.05435887739242418</v>
+        <v>-0.05497302249821701</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06594234980627078</v>
+        <v>-0.06544274415930573</v>
       </c>
     </row>
     <row r="12">
@@ -2498,49 +2498,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3468151718293555</v>
+        <v>-0.3473818939881639</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1120435755649964</v>
+        <v>-0.1126896204598467</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3677530336417121</v>
+        <v>-0.3683401080518607</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3746526327914594</v>
+        <v>-0.3752366591632494</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2460733515393301</v>
+        <v>-0.2466967118304098</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1108581671241566</v>
+        <v>-0.1115121164235049</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.03102066271743098</v>
+        <v>-0.03169606750169152</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1443171457040577</v>
+        <v>0.1435914813643251</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.223017093747238</v>
+        <v>0.2222705256394946</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2172418183520435</v>
+        <v>0.2164857156174236</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1776762339766051</v>
+        <v>0.1769271667079479</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0500392701060477</v>
+        <v>0.0493224024181842</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.05384816420605176</v>
+        <v>-0.05454449086187907</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09213428140445501</v>
+        <v>-0.09156477787721684</v>
       </c>
     </row>
     <row r="13">
@@ -2550,49 +2550,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3107484388069963</v>
+        <v>-0.3113902989501014</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1171270265614055</v>
+        <v>-0.1178402008124095</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3468889710003111</v>
+        <v>-0.3475499344006749</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3544759920118068</v>
+        <v>-0.3551335957671284</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2982987853827552</v>
+        <v>-0.2989783219009539</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1133859659245786</v>
+        <v>-0.1141084701906152</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.03271730239863047</v>
+        <v>-0.033461715910029</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1458684148965546</v>
+        <v>0.1450720695505368</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2505596519292936</v>
+        <v>0.2497356195395994</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1984805173410962</v>
+        <v>0.1976575465137387</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1091514605391097</v>
+        <v>0.1083478655905949</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.005203451001314363</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1216263186707636</v>
+        <v>-0.1223776223776269</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1867043161587816</v>
+        <v>-0.1860551991617285</v>
       </c>
     </row>
     <row r="14">
@@ -2602,49 +2602,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3202652933711576</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1121329911599886</v>
+        <v>-0.1129513481087301</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3151948091933576</v>
+        <v>-0.3159681166950321</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4001618583083584</v>
+        <v>-0.4009119109363155</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2631008983617349</v>
+        <v>-0.2638946608630945</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.07903855641391999</v>
+        <v>-0.07987490884139703</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.04802703094922833</v>
+        <v>-0.04887302549570904</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05907569188691042</v>
+        <v>0.0581946692003612</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.08857812407211441</v>
+        <v>0.08768819723196941</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.06804317908262192</v>
+        <v>0.06714469090084663</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.03054493815808002</v>
+        <v>0.02965234725201782</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.09919506940361345</v>
+        <v>-0.1000544870483751</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2245899955565349</v>
+        <v>-0.2254244856032344</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3176136419143916</v>
+        <v>-0.3168463734492022</v>
       </c>
     </row>
     <row r="15">
@@ -2654,49 +2654,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.274920751602636</v>
+        <v>-0.2757878254061481</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1542679619069176</v>
+        <v>-0.1551952243932533</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.253024083445446</v>
+        <v>-0.2539335391382451</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4425227843707162</v>
+        <v>-0.4433817494197214</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3765981445718154</v>
+        <v>-0.3774841190925855</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.142193841530613</v>
+        <v>-0.1431351334115973</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.16156192485915</v>
+        <v>-0.1625002361921943</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.02760970682618336</v>
+        <v>0.02661395434196834</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08359520579098501</v>
+        <v>0.08258348251745673</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.01889601536269225</v>
+        <v>0.0178851715461974</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.008560933520591618</v>
+        <v>0.007548570873581184</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1483401264103108</v>
+        <v>-0.1493120287450651</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2968953087438493</v>
+        <v>-0.2978370449130736</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4186697617375259</v>
+        <v>-0.41777855428046</v>
       </c>
     </row>
     <row r="16">
@@ -2709,46 +2709,46 @@
         <v>3848</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2395523098472836</v>
+        <v>-0.2405637901821152</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1272974993830971</v>
+        <v>-0.1283715536499912</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3267339316318925</v>
+        <v>-0.3277649310015747</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4676311369273876</v>
+        <v>-0.4686234814056078</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3696669794969054</v>
+        <v>-0.3706962792813471</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2137196249867586</v>
+        <v>-0.2147838052379214</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.154603605061439</v>
+        <v>-0.1556854018366423</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.03664795974827939</v>
+        <v>-0.03777049895870732</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.02050528904887017</v>
+        <v>0.01936610195228639</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.03625608681889503</v>
+        <v>-0.0373985689492855</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.07061008830920912</v>
+        <v>-0.07174843007231857</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2294699051888287</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3752924607195993</v>
+        <v>-0.376360727511404</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.489396492268682</v>
+        <v>-0.4998261279668341</v>
       </c>
     </row>
     <row r="17">
@@ -2761,46 +2761,46 @@
         <v>3808</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3730194720424365</v>
+        <v>-0.374137700254316</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1641897284085871</v>
+        <v>-0.1654005529175606</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4139717869683111</v>
+        <v>-0.4151269778478479</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5053361788950426</v>
+        <v>-0.5064650227009508</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4007111960300449</v>
+        <v>-0.4018805429587999</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2462555394346424</v>
+        <v>-0.2474590664225289</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2118585930348971</v>
+        <v>-0.2130737232452375</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.03532746731895742</v>
+        <v>-0.03660036374821374</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.05563291582202368</v>
+        <v>-0.05690254583419829</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1303270090444073</v>
+        <v>-0.1315974642779096</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1366700126368556</v>
+        <v>-0.1379442151962422</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2450692831508476</v>
+        <v>-0.2463148815319371</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3617527412975292</v>
+        <v>-0.3629781391592104</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4534179636430906</v>
+        <v>-0.4638475993412428</v>
       </c>
     </row>
     <row r="18">
@@ -2813,46 +2813,46 @@
         <v>3750</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.340328272363088</v>
+        <v>-0.3416654326071651</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2629486521319606</v>
+        <v>-0.2643509274259372</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.430731703600614</v>
+        <v>-0.4321008415093033</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5521228516698358</v>
+        <v>-0.5534568754031568</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5440253055244781</v>
+        <v>-0.5453768643888779</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3651982138517482</v>
+        <v>-0.3665899659263658</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.222497051312871</v>
+        <v>-0.2239298237492875</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.009394739455103718</v>
+        <v>-0.01089773685878015</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.002426290751657234</v>
+        <v>-0.003933569771852774</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1717038612056427</v>
+        <v>-0.1731900348608946</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1483383302165606</v>
+        <v>-0.1498370887221441</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.232288933477399</v>
+        <v>-0.2337651442789479</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3442737497008892</v>
+        <v>-0.345732366105878</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="19">
@@ -2865,46 +2865,46 @@
         <v>3674</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4858420098464364</v>
+        <v>-0.4874253877353283</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4550797757793887</v>
+        <v>-0.4567250210479941</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6182302597491045</v>
+        <v>-0.6198450144590524</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8263204205491448</v>
+        <v>-0.8278752920178434</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8341758270698136</v>
+        <v>-0.8357470408581165</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6578765481710107</v>
+        <v>-0.6594867562319848</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5105578930964612</v>
+        <v>-0.5122117644707131</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2019367845094564</v>
+        <v>-0.2036907173653333</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.247993607310562</v>
+        <v>-0.2497379317369948</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1856968368912675</v>
+        <v>-0.187486911015192</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.184822317864203</v>
+        <v>-0.1866202811510647</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2712300231097302</v>
+        <v>-0.2730042820271805</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3496303093089494</v>
+        <v>-0.3513979754581271</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3993101746374492</v>
+        <v>-0.4097398103356014</v>
       </c>
     </row>
     <row r="20">
@@ -2917,46 +2917,46 @@
         <v>3603</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1269838502404141</v>
+        <v>-0.1289514483539449</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2290429409261776</v>
+        <v>-0.2310448304899637</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4428327306043869</v>
+        <v>-0.4447915592945222</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7408186428973877</v>
+        <v>-0.7426910122309351</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7656269987663862</v>
+        <v>-0.7675140951458701</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4254626603513145</v>
+        <v>-0.4274336582448583</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3288309370568783</v>
+        <v>-0.3308330058064968</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1153802511005111</v>
+        <v>-0.1174604404882444</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.07789271879475024</v>
+        <v>-0.07998672278728947</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.03067955207853856</v>
+        <v>0.02852175919769451</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.04748361722270289</v>
+        <v>-0.04962868718586577</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.04085510878097409</v>
+        <v>-0.02740282006086403</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.01071931163688333</v>
+        <v>0.02427535798848623</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.07261514293112015</v>
+        <v>-0.08304477862927229</v>
       </c>
     </row>
     <row r="21">
@@ -2969,46 +2969,46 @@
         <v>3531</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2617999021308819</v>
+        <v>-0.2640281457560434</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3327598845729298</v>
+        <v>-0.3350399767055308</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6559009902513182</v>
+        <v>-0.6581083204470275</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.962785550703039</v>
+        <v>-0.964901615188829</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9204921611495251</v>
+        <v>-0.9226450142699392</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5512008439257698</v>
+        <v>-0.5534462411666468</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3659686851537387</v>
+        <v>-0.3682714186373204</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1667695841286658</v>
+        <v>-0.169150474753188</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1555736168804884</v>
+        <v>-0.1579616172888407</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.02943797242459567</v>
+        <v>0.02695887387578466</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.005391817483463512</v>
+        <v>0.008065476226754242</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1139531070667275</v>
+        <v>0.1274053957868375</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1751485102821206</v>
+        <v>0.1887045566337235</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.02825958253364291</v>
+        <v>-0.03868921823179505</v>
       </c>
     </row>
     <row r="22">
@@ -3021,46 +3021,46 @@
         <v>3439</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1442503851751695</v>
+        <v>-0.146906172604524</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2030682139981366</v>
+        <v>-0.2057912187257926</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4952375753483054</v>
+        <v>-0.4978975872624218</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6686115419964125</v>
+        <v>-0.6712159793905172</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6687920439544257</v>
+        <v>-0.6714255811406744</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4136854949467903</v>
+        <v>-0.416379219235921</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.04688030423255185</v>
+        <v>-0.04968638806671777</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.08304424822034662</v>
+        <v>0.08017483097613365</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1253134225464123</v>
+        <v>0.1224270591445134</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3380986292629728</v>
+        <v>0.3351049930782963</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3368928478357773</v>
+        <v>0.3503501415459951</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5166671072457589</v>
+        <v>0.530119395965869</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.5907422433203422</v>
+        <v>0.6042982896719451</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.3752120489900577</v>
+        <v>0.3647824132919055</v>
       </c>
     </row>
     <row r="23">
@@ -3070,205 +3070,205 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3000632083030865</v>
+        <v>-0.3173827568846974</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1647134257115397</v>
+        <v>-0.18165436240416</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3344581255874886</v>
+        <v>-0.3513106537697581</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3672380209028745</v>
+        <v>-0.3841274567600763</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.650504652919679</v>
+        <v>-0.6672713507855548</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3966199345497259</v>
+        <v>-0.4134634698154258</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.01671568863814343</v>
+        <v>-0.03354480055590159</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1903469128235145</v>
+        <v>0.1736236158986557</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1159916185686427</v>
+        <v>0.09927710595296446</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3895467194190303</v>
+        <v>0.373029644797775</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2745600019237173</v>
+        <v>0.2750130939871269</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4585541706395873</v>
+        <v>0.4590470380215876</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.606821402902348</v>
+        <v>0.6075881930889011</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3777874987932393</v>
+        <v>0.3544253099421937</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.09649</t>
+          <t>X &gt; -0.09648</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3244</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.01194132934428893</v>
+        <v>0.008327976841179918</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1692808097531966</v>
+        <v>0.165506237914272</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.160223943434346</v>
+        <v>0.1564229246111069</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1226801851443753</v>
+        <v>0.1188976210856438</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.275854200844293</v>
+        <v>-0.2795533024759393</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.02316836087451435</v>
+        <v>-0.0269267691118884</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4016721252482327</v>
+        <v>0.3977750135921099</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5367983421867066</v>
+        <v>0.5328252639418309</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3696965522271398</v>
+        <v>0.3657686059265188</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6464496718659802</v>
+        <v>0.6423755703528116</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5033486286827937</v>
+        <v>0.5168059223930115</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.6610363482970385</v>
+        <v>0.6744886370171486</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.857304548696149</v>
+        <v>0.8708605950477519</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.7679383347332305</v>
+        <v>0.7575086990350783</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.08772</t>
+          <t>X &gt; -0.08771</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3143</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.04463274577987164</v>
+        <v>0.04049215214880775</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1634742616845486</v>
+        <v>0.1591669119348111</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.3255161856260003</v>
+        <v>0.321123952770229</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4096675071269331</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04747859669716092</v>
+        <v>0.04313766168851174</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.298830775060722</v>
+        <v>0.2944310291824195</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7719195109224515</v>
+        <v>0.7673603251171954</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9583028084883907</v>
+        <v>0.9536450298913692</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9151530580278049</v>
+        <v>0.9105016612608523</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.260108584690869</v>
+        <v>1.255277784367713</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.118988731579137</v>
+        <v>1.132446025289354</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.24882209573336</v>
+        <v>1.26227438445347</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.369451990038215</v>
+        <v>1.383008036389818</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.364639437491086</v>
+        <v>1.354209801792933</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.07895</t>
+          <t>X &gt; -0.07894</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3029</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1727894612251859</v>
+        <v>0.1679816331708111</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3566278429205951</v>
+        <v>0.3516108454604066</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4408308226797786</v>
+        <v>0.4357474992200352</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.457390614747716</v>
+        <v>0.4523107920203842</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1347990035390652</v>
+        <v>0.1297737790093052</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4833595854109234</v>
+        <v>0.4782436266064423</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.010464247548263</v>
+        <v>1.005163932528141</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.287492595632258</v>
+        <v>1.282055525608172</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.17911647727049</v>
+        <v>1.173706624914125</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.569137426367362</v>
+        <v>1.563518532106613</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.430412494258434</v>
+        <v>1.443869787968652</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.530824043812515</v>
+        <v>1.544276332532625</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.671810766641137</v>
+        <v>1.68536681299274</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.657418530082822</v>
+        <v>1.64698889438467</v>
       </c>
     </row>
     <row r="27">
@@ -3281,46 +3281,46 @@
         <v>2892</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2651823694451991</v>
+        <v>0.2595183024542749</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.4655296328830332</v>
+        <v>0.4596220143328509</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1930110096425679</v>
+        <v>0.187152017690245</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3076248228332261</v>
+        <v>0.3017367284028438</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.0392641918487513</v>
+        <v>-0.04509325096376671</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4498422655665237</v>
+        <v>0.4438725758629332</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8678937760240686</v>
+        <v>0.8617672032855666</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.214938940767553</v>
+        <v>1.208639140511536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.311745922787658</v>
+        <v>1.305402570588065</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.637277722545342</v>
+        <v>1.650682850198173</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.501680691450446</v>
+        <v>1.515137985160663</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.605220142018567</v>
+        <v>1.618672430738677</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.772794023466474</v>
+        <v>1.786350069818077</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.849624622686051</v>
+        <v>1.839194986987899</v>
       </c>
     </row>
     <row r="28">
@@ -3333,46 +3333,46 @@
         <v>2704</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.5301604998490177</v>
+        <v>0.523138521621938</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8193702136350609</v>
+        <v>0.8120276699121476</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4816691757273333</v>
+        <v>0.4743953961100829</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.263078288333169</v>
+        <v>0.2558977606963992</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.03360263656341544</v>
+        <v>-0.04074817994988678</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2841106148152264</v>
+        <v>0.2768821974466107</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9587614937732951</v>
+        <v>0.9512684196675849</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.25152415857611</v>
+        <v>1.243857404360952</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.285351952889059</v>
+        <v>1.277660164768164</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.507711974961722</v>
+        <v>1.521117102614554</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.302958650644143</v>
+        <v>1.316415944354361</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.559235299113837</v>
+        <v>1.572687587833947</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.730696664500293</v>
+        <v>1.744252710851896</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.869471251214449</v>
+        <v>1.859041615516297</v>
       </c>
     </row>
     <row r="29">
@@ -3382,49 +3382,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5856240556342769</v>
+        <v>0.5794973239966481</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.061919704345648</v>
+        <v>1.074829513921699</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.251610413907116</v>
+        <v>0.2646175453247182</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.04564695584383571</v>
+        <v>0.05862609824229992</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.4839130764115467</v>
+        <v>0.497023880786486</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.763597037136222</v>
+        <v>0.7766399334305873</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.258462763839113</v>
+        <v>1.231704247132015</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.650225103410456</v>
+        <v>1.623565475255496</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.611868799932019</v>
+        <v>1.585211022346321</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.798013044955894</v>
+        <v>1.794620589680797</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.672972753719222</v>
+        <v>1.669664248007528</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.866781977226466</v>
+        <v>1.863532033536686</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.044375114388387</v>
+        <v>2.041467304625201</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.054957347421947</v>
+        <v>2.027968505090961</v>
       </c>
     </row>
     <row r="30">
@@ -3437,150 +3437,150 @@
         <v>2301</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8659028154640538</v>
+        <v>0.8784251051396765</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.402360139679189</v>
+        <v>1.391209536566535</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7906657609230194</v>
+        <v>0.8036728923406216</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4676826880644427</v>
+        <v>0.4568815571779012</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.864520722208951</v>
+        <v>0.8534351840917225</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.161962659924612</v>
+        <v>1.175005556218977</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.492240913752831</v>
+        <v>1.480920196952809</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.135477837045855</v>
+        <v>2.123779123484987</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.142838664352297</v>
+        <v>2.131117176351758</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.248819520176184</v>
+        <v>2.262224647829015</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.08752556135186</v>
+        <v>2.100982855062078</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.51304300813667</v>
+        <v>2.52649529685678</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.310085224658089</v>
+        <v>2.323641271009691</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.559806556934376</v>
+        <v>2.549376921236224</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.03509</t>
+          <t>X &gt; -0.03508</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2064</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.229965935109178</v>
+        <v>1.2424882247848</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.987831393711645</v>
+        <v>2.000741203287696</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7709123969796678</v>
+        <v>0.78391952839727</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7343879742106481</v>
+        <v>0.7207210743067094</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.8248975767485405</v>
+        <v>0.8380083811234798</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.460994570100397</v>
+        <v>1.474037466394762</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.226247107113991</v>
+        <v>2.211775099387907</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.077185542525662</v>
+        <v>2.062660980938468</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.479964585337115</v>
+        <v>2.46521974638771</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.598831648371203</v>
+        <v>2.612236776024034</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.73322561087533</v>
+        <v>2.746682904585548</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.203655279848661</v>
+        <v>3.217107568568771</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.831850281306856</v>
+        <v>2.845406327658459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.42071890040485</v>
+        <v>3.410289264706698</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.02632</t>
+          <t>X &gt; -0.02631</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1782</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6455751327048205</v>
+        <v>0.6580974223804432</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.556423044404241</v>
+        <v>1.569332853980292</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6010162212157226</v>
+        <v>0.6140233526333247</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.5070541071864554</v>
+        <v>0.5200332495849196</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5852248203654042</v>
+        <v>0.5983356247403435</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.387151063013803</v>
+        <v>1.400193959308169</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.367439767266191</v>
+        <v>2.380506021566667</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.661368415747205</v>
+        <v>2.642136929349427</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.193984630752503</v>
+        <v>3.174419764313257</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.578427346959145</v>
+        <v>3.591832474611977</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.542024190991739</v>
+        <v>3.555481484701957</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.249808021737842</v>
+        <v>4.263260310457952</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.94178685635972</v>
+        <v>3.955342902711322</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.528208525336339</v>
+        <v>4.517778889638187</v>
       </c>
     </row>
     <row r="33">
@@ -3593,98 +3593,98 @@
         <v>1483</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.9745751478034919</v>
+        <v>0.9870974374791146</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.383203555041256</v>
+        <v>1.396113364617307</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.9165677790319577</v>
+        <v>0.9295469214304219</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.118887304700536</v>
+        <v>1.131998109075475</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.483669309756266</v>
+        <v>1.496712206050631</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.611056804605198</v>
+        <v>2.624123058905674</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.0585003581865</v>
+        <v>3.032475290539807</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.913360906433574</v>
+        <v>3.886709992630117</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.018731338398219</v>
+        <v>5.03213646605105</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.948839780769781</v>
+        <v>4.962297074479999</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.062117071628364</v>
+        <v>6.075569360348474</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.304708043960602</v>
+        <v>5.318264090312205</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.026445559648899</v>
+        <v>6.016015923950746</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.008772</t>
+          <t>X &gt; -0.008771</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4795346527630002</v>
+        <v>0.492056942438623</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.381474553312252</v>
+        <v>2.394384362888303</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.527146387256202</v>
+        <v>2.540153518673804</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.936678799142989</v>
+        <v>1.949657941541453</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.218077403890639</v>
+        <v>1.231188208265579</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.785789611876567</v>
+        <v>1.798832508170932</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.052407245955635</v>
+        <v>3.065473500256111</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.206845468795763</v>
+        <v>4.220026478091</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.740407683036693</v>
+        <v>4.699584862108757</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.874051659415436</v>
+        <v>5.887456787068267</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.84964098613483</v>
+        <v>5.863098279845048</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.515223422109656</v>
+        <v>6.528675710829766</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.373598207016869</v>
+        <v>5.387154253368472</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.164347492404076</v>
+        <v>6.153917856705924</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3855,46 +3855,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.54773840784823</v>
+        <v>14.56074553926583</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19.43989630236049</v>
+        <v>19.45287544475895</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.90147508728832</v>
+        <v>18.91458589166326</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.8179646440516</v>
+        <v>16.83100754034596</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.35227854582694</v>
+        <v>14.36534480012742</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.47026657552972</v>
+        <v>4.48371886424983</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3907,46 +3907,46 @@
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.48594312308899</v>
+        <v>13.49846541276461</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.781586004970094</v>
+        <v>8.794495814546146</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.51042863857968</v>
+        <v>12.52343576999728</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>16.76439311139338</v>
+        <v>16.77737225379185</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>16.22597189632121</v>
+        <v>16.23908270069615</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>14.46155816393377</v>
+        <v>14.47460106022814</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.31496877655839</v>
+        <v>12.32803503085887</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.724074037570716</v>
+        <v>7.737255046865954</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.570290646233779</v>
+        <v>4.583489385188543</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.751093296257395</v>
+        <v>4.764498423910226</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.453556466785173</v>
+        <v>1.467013760495391</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.518867459182161</v>
+        <v>2.532319747902271</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.067685013185702</v>
+        <v>1.081241059537305</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.31740634546199</v>
+        <v>1.306976709763838</v>
       </c>
     </row>
     <row r="8">
@@ -3959,98 +3959,98 @@
         <v>103</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13.52597915551819</v>
+        <v>13.53850144519381</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.030910396922849</v>
+        <v>8.0438202064989</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.4904106223651</v>
+        <v>12.50341775378271</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.5332851141959</v>
+        <v>15.54626425659436</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>15.96573768553149</v>
+        <v>15.97884848990643</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>13.35055826402386</v>
+        <v>13.36360116031823</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.32407697393605</v>
+        <v>11.33714322823653</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.94427221593125</v>
+        <v>7.957453225226487</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.999777184117868</v>
+        <v>4.012975923072631</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.091399571905477</v>
+        <v>5.104804699558308</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.003151101956831</v>
+        <v>1.016608395667049</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.008408045710027</v>
+        <v>2.021860334430137</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.588153434765125</v>
+        <v>1.601709481116728</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8670009806336481</v>
+        <v>0.8565713449354959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.2281</t>
+          <t>X &lt; -0.228</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>125</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.30656167979002</v>
+        <v>12.31908396946564</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.294988066825766</v>
+        <v>8.307897876401817</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.50011936022918</v>
+        <v>13.51312649164678</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.23037249283667</v>
+        <v>15.24335163523514</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12.29195127776451</v>
+        <v>12.30506208213945</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>10.98939321548018</v>
+        <v>11.00243611177454</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.9046594982079</v>
+        <v>10.91772575250837</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.637476099426387</v>
+        <v>5.650657108721624</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.321597703898576</v>
+        <v>1.335054997608793</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.955980861244008</v>
+        <v>2.969433149964118</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.135726250299108</v>
+        <v>4.149282296650711</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="10">
@@ -4063,46 +4063,46 @@
         <v>137</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12.47006532942505</v>
+        <v>12.48258761910068</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.398637701862263</v>
+        <v>9.411547511438314</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>13.38333103906129</v>
+        <v>13.39633817047889</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.97343818626734</v>
+        <v>14.9864173286658</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.97516295659662</v>
+        <v>12.98827376097156</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.08282387241448</v>
+        <v>11.09586676870885</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.72801716244147</v>
+        <v>11.74108341674194</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.42141770526581</v>
+        <v>5.434598714561048</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.630490811784242</v>
+        <v>4.643689550739005</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.510292634055581</v>
+        <v>4.523697761708412</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.845685295139461</v>
+        <v>2.859142588849679</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.339922467083433</v>
+        <v>4.353374755803543</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.379521870737072</v>
+        <v>5.393077917088675</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.899316195714086</v>
+        <v>4.888886560015933</v>
       </c>
     </row>
     <row r="11">
@@ -4115,46 +4115,46 @@
         <v>172</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10.29725935420863</v>
+        <v>10.30978164388425</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.522895043569953</v>
+        <v>7.535804853146004</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.03500308115942</v>
+        <v>10.04801021257702</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.74665156260412</v>
+        <v>10.75963070500259</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.464044301020323</v>
+        <v>8.477155105395262</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.435904843387142</v>
+        <v>6.448947739681508</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.351171126114863</v>
+        <v>6.364237380415339</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.395615634310111</v>
+        <v>2.408796643605349</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.009034352778968469</v>
+        <v>0.02223309173373167</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2596954834117469</v>
+        <v>-0.2462903557589158</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.116946541107886</v>
+        <v>0.1304038348181038</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.476911093802158</v>
+        <v>2.490363382522268</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.963633227043296</v>
+        <v>4.977189273394899</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.631959210482371</v>
+        <v>4.621529574784219</v>
       </c>
     </row>
     <row r="12">
@@ -4167,46 +4167,46 @@
         <v>195</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.869347041184746</v>
+        <v>4.882256850760797</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.089862949972762</v>
+        <v>9.102870081390364</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.73293659540078</v>
+        <v>9.745915737799244</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.143233329046559</v>
+        <v>7.156344133421499</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.876572702659658</v>
+        <v>4.889615598954023</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.766197959746357</v>
+        <v>3.779264214046833</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2907290287787347</v>
+        <v>-0.2775480194834969</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.201854099988964</v>
+        <v>-1.188448972336133</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.380966398665521</v>
+        <v>-0.3675091049553032</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.217519322782479</v>
+        <v>2.230971611502589</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.36136727594014</v>
+        <v>4.374923322291743</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.611088608216427</v>
+        <v>4.600658972518275</v>
       </c>
     </row>
     <row r="13">
@@ -4219,46 +4219,46 @@
         <v>215</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.111212842580727</v>
+        <v>6.12373513225635</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.49963922961647</v>
+        <v>4.512549039192521</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.825700755578019</v>
+        <v>7.838707886995621</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.42107016725528</v>
+        <v>8.434049309653744</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.41753267311335</v>
+        <v>7.430643477488289</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.459160657340632</v>
+        <v>4.472203553634998</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.444194381928824</v>
+        <v>3.4572606362293</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2788029703410473</v>
+        <v>-0.2656219610458095</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.735151693732661</v>
+        <v>-1.721952954777898</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7248117624815151</v>
+        <v>-0.711406634828684</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9309000294799716</v>
+        <v>0.9443573231901894</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.825748303104476</v>
+        <v>2.839200591824586</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.196191366578184</v>
+        <v>5.209747412929786</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.911028977924239</v>
+        <v>5.900599342226087</v>
       </c>
     </row>
     <row r="14">
@@ -4271,46 +4271,46 @@
         <v>245</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.465745353259408</v>
+        <v>5.47826764293503</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.854171740295151</v>
+        <v>3.867081549871202</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.316445890841422</v>
+        <v>6.329453022259024</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.079352084673417</v>
+        <v>8.092331227071881</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.908277808376752</v>
+        <v>5.921388612751691</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.348576888949552</v>
+        <v>3.361619785243917</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.263843171677273</v>
+        <v>3.276909425977749</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.164006711671284</v>
+        <v>1.177187720966522</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.103006825488983</v>
+        <v>1.116205564443746</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.477371436379428</v>
+        <v>1.490776564032259</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.088944642674093</v>
+        <v>2.102401936384311</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.164144126550134</v>
+        <v>4.177596415270244</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.192869107441965</v>
+        <v>6.206425153793568</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.258916970330496</v>
+        <v>7.248487334632344</v>
       </c>
     </row>
     <row r="15">
@@ -4323,46 +4323,46 @@
         <v>279</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.137386052549886</v>
+        <v>4.149908342225508</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.959504195858031</v>
+        <v>3.972414005434082</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.639904306465738</v>
+        <v>4.65291143788334</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.637540951618035</v>
+        <v>7.6505200940165</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.740696797477774</v>
+        <v>6.753807601852714</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.812332283580524</v>
+        <v>3.825375179874889</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.44444444444445</v>
+        <v>4.457510698744926</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.46830047218625</v>
+        <v>1.481481481481488</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.048877646935843</v>
+        <v>1.062076385890606</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.990867157248424</v>
+        <v>2.004272284901255</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.144536771998936</v>
+        <v>2.157994065709154</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.329457563752982</v>
+        <v>4.342909852473092</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.418163526284772</v>
+        <v>6.431719572636375</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.743153675765356</v>
+        <v>7.732724040067204</v>
       </c>
     </row>
     <row r="16">
@@ -4372,49 +4372,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.166939038280589</v>
+        <v>3.179461327956211</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.12769246934149</v>
+        <v>3.140602278917541</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.93408162438012</v>
+        <v>4.947088755797722</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.951127209817805</v>
+        <v>6.96410635221627</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.783775177135574</v>
+        <v>5.796885981510513</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.194424662021049</v>
+        <v>4.207467558315415</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.795225535943736</v>
+        <v>3.808291790244212</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.070180501942112</v>
+        <v>2.083361511237349</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.694715206954776</v>
+        <v>1.707913945909539</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.416917065952006</v>
+        <v>2.430322193604837</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.841094559244489</v>
+        <v>2.854551852954707</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.762270169420113</v>
+        <v>4.775722458140223</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.543273420110431</v>
+        <v>6.556829466462034</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.623302472165307</v>
+        <v>7.725961343103656</v>
       </c>
     </row>
     <row r="17">
@@ -4424,49 +4424,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.210472294315167</v>
+        <v>4.22299458399079</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.157557899228003</v>
+        <v>3.170467708804054</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.276655673078338</v>
+        <v>5.28966280449594</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.524227241440023</v>
+        <v>6.537206383838488</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.427146808490768</v>
+        <v>5.440257612865707</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.048611092575143</v>
+        <v>4.061653988869509</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.963877375302864</v>
+        <v>3.97694362960334</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.820716322890071</v>
+        <v>1.833897332185309</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.318375654584869</v>
+        <v>2.331574393539633</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.144228123188235</v>
+        <v>3.157633250841066</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.218804407809188</v>
+        <v>3.232261701519406</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.370506000908819</v>
+        <v>4.383958289628929</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.626229043595195</v>
+        <v>5.639785089946798</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.330545621791082</v>
+        <v>6.424179958050431</v>
       </c>
     </row>
     <row r="18">
@@ -4476,49 +4476,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.275792449020798</v>
+        <v>3.288314738696421</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.587295759133454</v>
+        <v>3.600205568709505</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.634734744844565</v>
+        <v>4.647741876262167</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.966910954375138</v>
+        <v>5.979890096773602</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.909258970072194</v>
+        <v>5.922369774447134</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.524008600095556</v>
+        <v>4.537051496389921</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.477736421284817</v>
+        <v>3.490802675585293</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.327860714811003</v>
+        <v>1.34104172410624</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.507245444013314</v>
+        <v>1.520444182968077</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.060966412831547</v>
+        <v>3.074371540484378</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.856213088513968</v>
+        <v>2.869670382224186</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.611750092013239</v>
+        <v>3.625202380733349</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.633803173376037</v>
+        <v>4.64735921972764</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.031230715105515</v>
+        <v>5.113479485338786</v>
       </c>
     </row>
     <row r="19">
@@ -4528,49 +4528,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.807374687920102</v>
+        <v>3.819896977595725</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.431573432679421</v>
+        <v>4.444483242255473</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.256216921204782</v>
+        <v>5.269224052622384</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.012486313974883</v>
+        <v>7.025465456373347</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.083821196463688</v>
+        <v>7.096932000838628</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.958498906537081</v>
+        <v>5.971541802831446</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.060757059183494</v>
+        <v>5.07382331348397</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.56105333519875</v>
+        <v>2.574234344493988</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.666188426590146</v>
+        <v>2.679593554242977</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.664687134792892</v>
+        <v>2.67814442850311</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.308826389699298</v>
+        <v>3.322278678419408</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.904831941356022</v>
+        <v>3.918387987707625</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.074245953247498</v>
+        <v>4.144123637934158</v>
       </c>
     </row>
     <row r="20">
@@ -4580,49 +4580,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9578891134183394</v>
+        <v>0.9704114030939621</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.355165057976215</v>
+        <v>2.368074867552266</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.376225554919444</v>
+        <v>3.389232686337046</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.453381342394202</v>
+        <v>5.466360484792666</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.622924729091935</v>
+        <v>5.636035533466874</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.619481711055386</v>
+        <v>3.632524607349751</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.180765692898156</v>
+        <v>3.193831947198632</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.651635391461781</v>
+        <v>1.664816400757019</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.590635505279479</v>
+        <v>1.603834244234243</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9175014706940416</v>
+        <v>0.9309065983468727</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.420712748146364</v>
+        <v>1.434170041856582</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.380094336421323</v>
+        <v>1.29155704376943</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.062191614419895</v>
+        <v>0.9733957718280237</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.414629077237315</v>
+        <v>1.479103204426089</v>
       </c>
     </row>
     <row r="21">
@@ -4632,49 +4632,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.581796789507891</v>
+        <v>1.594319079183514</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.634799979051472</v>
+        <v>2.647709788627523</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.120809015401584</v>
+        <v>4.133816146819186</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.975200079043574</v>
+        <v>5.988179221442039</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.750258487795854</v>
+        <v>5.763369292170793</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.853343058740357</v>
+        <v>3.866385955034723</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.984910281906949</v>
+        <v>2.997976536207425</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.734027823564325</v>
+        <v>1.747208832859563</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.829767749294241</v>
+        <v>1.842966488249004</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8229027523540964</v>
+        <v>0.8363078800069275</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.021440718027307</v>
+        <v>0.945086345571184</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3597544461496724</v>
+        <v>0.2843468077349272</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.02863963612588094</v>
+        <v>-0.04694411844362634</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9986967939318632</v>
+        <v>1.055332907507164</v>
       </c>
     </row>
     <row r="22">
@@ -4684,49 +4684,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.794232912666736</v>
+        <v>0.8067552023423588</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.648412724360014</v>
+        <v>1.661322533936065</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.760393332831917</v>
+        <v>2.773400464249519</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.712564273658593</v>
+        <v>3.725543416057057</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.722088264065881</v>
+        <v>3.735199068440821</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.649667188082908</v>
+        <v>2.662710084377274</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.058084155742137</v>
+        <v>1.071150410042613</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3169281542209106</v>
+        <v>0.3301091635161484</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.255928268038609</v>
+        <v>0.2691270069933722</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7311832183591847</v>
+        <v>-0.7177780907063536</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7854929475966799</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.573689468426323</v>
+        <v>-1.635230773218318</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.918744176110785</v>
+        <v>-1.980388033019622</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.042651590978316</v>
+        <v>-0.9916945703167031</v>
       </c>
     </row>
     <row r="23">
@@ -4736,205 +4736,205 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.315509684626775</v>
+        <v>1.383818268982552</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.275882867309441</v>
+        <v>1.342680485097475</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.727447050676581</v>
+        <v>1.793319728361752</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.978619167564609</v>
+        <v>2.044317818810015</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.133063732419892</v>
+        <v>3.196849521752974</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.22131582733023</v>
+        <v>2.286494082789027</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.8064732829720995</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1443860529315302</v>
+        <v>-0.07687912316242773</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2782899980082973</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8136731555806946</v>
+        <v>-0.746234182295261</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3461989062709137</v>
+        <v>-0.347070606255933</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.092503987240839</v>
+        <v>-1.091510018113262</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.688545594361081</v>
+        <v>-1.687037315940088</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8859983469507213</v>
+        <v>-0.7886184167591139</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.09649</t>
+          <t>X &lt; -0.09648</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.047102220330558</v>
+        <v>0.05962451000618074</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.05095787912017613</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2296103695005485</v>
+        <v>-0.2166032380829463</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.008750871215056577</v>
+        <v>0.02173001361352078</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.416275602088831</v>
+        <v>1.42938640646377</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.632636458723411</v>
+        <v>0.6456793550177764</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.749394555846159</v>
+        <v>-0.736328301545683</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.324686062735765</v>
+        <v>-1.311505053440527</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6289291921613227</v>
+        <v>-0.6157304532065595</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.587162485297355</v>
+        <v>-1.573757357644524</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.08359710129622</v>
+        <v>-1.129809867256064</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.639468759557715</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.325878955774641</v>
+        <v>-2.371194409741484</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.125735913624382</v>
+        <v>-2.086587259196506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.08772</t>
+          <t>X &lt; -0.08771</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.05679114672069119</v>
+        <v>-0.04426885704506844</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.01144468171224133</v>
+        <v>0.001465127863809812</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.698711049127553</v>
+        <v>-0.6857039177099509</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8608555773387607</v>
+        <v>-0.8478764349402965</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2576432855617838</v>
+        <v>0.2707540899367231</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4195736461182733</v>
+        <v>-0.4065307498239079</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.77136389360497</v>
+        <v>-1.758297639304494</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.433479066265619</v>
+        <v>-2.420298056970381</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.202081291629206</v>
+        <v>-2.188882552674443</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.247138250536274</v>
+        <v>-3.233733122883443</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.814987661955072</v>
+        <v>-2.853638959506213</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.216675388755988</v>
+        <v>-3.254957093938316</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.585094864070392</v>
+        <v>-3.623373953349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.674826390027341</v>
+        <v>-3.639058299457069</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.07895</t>
+          <t>X &lt; -0.07894</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3881751623152425</v>
+        <v>-0.3756528726396198</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5085207051040541</v>
+        <v>-0.495610895528003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.903389411700644</v>
+        <v>-0.8903822802830419</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8608555773387607</v>
+        <v>-0.8478764349402965</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.004231979518898754</v>
+        <v>0.01734278389383803</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8386769599584269</v>
+        <v>-0.8256340636640616</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.151480852669309</v>
+        <v>-2.138414598368833</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.969541444433261</v>
+        <v>-2.956360435138023</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-2.578746100432731</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.617508620906648</v>
+        <v>-3.604103493253817</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.249429512958308</v>
+        <v>-3.282488862040324</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.519941810109245</v>
+        <v>-3.552779317112261</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.893825200888223</v>
+        <v>-3.926640374702544</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.949763685030241</v>
+        <v>-3.918385747054153</v>
       </c>
     </row>
     <row r="27">
@@ -4944,49 +4944,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5372567865636597</v>
+        <v>-0.524734496888037</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6621324339566996</v>
+        <v>-0.6492226243806485</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1962812657489152</v>
+        <v>-0.1832741343313131</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3790171785248262</v>
+        <v>-0.366038036126362</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4127650492825055</v>
+        <v>0.4258758536574447</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6199964558813349</v>
+        <v>-0.6069535595869695</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.487202786612137</v>
+        <v>-1.474136532311661</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.345622492122907</v>
+        <v>-2.332441482827669</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.484869639651066</v>
+        <v>-2.471670900696303</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.215387421274841</v>
+        <v>-3.243342435680304</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.908496339988567</v>
+        <v>-2.936832238099896</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.14597992306971</v>
+        <v>-3.174140517747482</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.524556324269177</v>
+        <v>-3.552678487663009</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.782973470056184</v>
+        <v>-3.756222241505803</v>
       </c>
     </row>
     <row r="28">
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9245433679589539</v>
+        <v>-0.9120210782833311</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.171860500704931</v>
+        <v>-1.158950691128879</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6799624951596357</v>
+        <v>-0.6669553637420336</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2086452424975676</v>
+        <v>-0.1956661000991033</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3443387266048887</v>
+        <v>0.357449530979828</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1767732238104216</v>
+        <v>-0.1637303275160562</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.352912125257319</v>
+        <v>-1.339845870956843</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.956521172060654</v>
+        <v>-1.943340162765416</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.949308234232042</v>
+        <v>-1.936109495277279</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.353512453012506</v>
+        <v>-2.376751347541649</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.975123607576826</v>
+        <v>-1.998733398295641</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.450444292549562</v>
+        <v>-2.473736248942977</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.765504939851375</v>
+        <v>-2.78879015721121</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.094908338026926</v>
+        <v>-3.073408865708252</v>
       </c>
     </row>
     <row r="29">
@@ -5048,49 +5048,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.837809181137132</v>
+        <v>-0.8272780269264146</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.305493570741959</v>
+        <v>-1.324352424440541</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1952448781814198</v>
+        <v>-0.2149120161751199</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>0.1559870142965138</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4830035687135137</v>
+        <v>-0.5026394822408164</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8478132866269945</v>
+        <v>-0.8671186415347236</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.534593963562124</v>
+        <v>-1.493345246288264</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.182391450242484</v>
+        <v>-2.14091930523746</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.062777248525926</v>
+        <v>-2.021396046597779</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.338709212747688</v>
+        <v>-2.329798597440266</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.149408926601716</v>
+        <v>-2.140923328700651</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.444260393279507</v>
+        <v>-2.435386127144312</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.711346773237402</v>
+        <v>-2.702556160251035</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.791364011627493</v>
+        <v>-2.745850569407438</v>
       </c>
     </row>
     <row r="30">
@@ -5100,153 +5100,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.023636075421088</v>
+        <v>-1.038608338226666</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.459367892554248</v>
+        <v>-1.446458082978197</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.810041067578311</v>
+        <v>-0.8257297349700039</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3589323199975425</v>
+        <v>-0.3459531775990783</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8438775992408409</v>
+        <v>-0.8307667948659017</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.159563445836042</v>
+        <v>-1.175103995177338</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.511819902541177</v>
+        <v>-1.498753648240701</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.35353513652867</v>
+        <v>-2.340354127233432</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.307525926937828</v>
+        <v>-2.294327187983065</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.433392012469056</v>
+        <v>-2.448686861787507</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.234481567660069</v>
+        <v>-2.249955709029322</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.760632214854603</v>
+        <v>-2.77582662507605</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.508777771148608</v>
+        <v>-2.524243962727638</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.873779885235763</v>
+        <v>-2.859298407010151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.03509</t>
+          <t>X &lt; -0.03508</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.166424102200494</v>
+        <v>-1.178215888421605</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.710512170253409</v>
+        <v>-1.722433877152682</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6099375657670265</v>
+        <v>-0.6224828018572524</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5271227633303042</v>
+        <v>-0.51414362093184</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6128422675605947</v>
+        <v>-0.6254882024905299</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.19180336571641</v>
+        <v>-1.204113484808289</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.893821033605981</v>
+        <v>-1.880754779305505</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.791203862586904</v>
+        <v>-1.778022853291667</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.137104033669488</v>
+        <v>-2.123905294714724</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.249420943280278</v>
+        <v>-2.261573378793884</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.38106389305959</v>
+        <v>-2.393211035645365</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.844114240990891</v>
+        <v>-2.856042135206984</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.477784691660922</v>
+        <v>-2.489994926364027</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.106603821517893</v>
+        <v>-3.094820302409154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.02632</t>
+          <t>X &lt; -0.02631</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4466546944789798</v>
+        <v>-0.4558638384675504</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9499764129067856</v>
+        <v>-0.9592700433976802</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3192786330818649</v>
+        <v>-0.3289127895901629</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2081887785978651</v>
+        <v>-0.217852378142787</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2636972578003451</v>
+        <v>-0.273440636388365</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8224108866546089</v>
+        <v>-0.8318735116564255</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.512760937303</v>
+        <v>-1.521956122753252</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.770564101578643</v>
+        <v>-1.757383092283405</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.124696316069141</v>
+        <v>-2.111497577114378</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.407959822223724</v>
+        <v>-2.417027763728996</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.38066549811316</v>
+        <v>-2.389787901427646</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.910685805422652</v>
+        <v>-2.919586129164131</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.679374420841832</v>
+        <v>-2.688453552405889</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.162349312095181</v>
+        <v>-3.153169972585836</v>
       </c>
     </row>
     <row r="33">
@@ -5256,101 +5256,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.5068063112979857</v>
+        <v>-0.5135812124200214</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.5760371932039519</v>
+        <v>-0.5830044629966267</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4679222599863593</v>
+        <v>-0.4749864355448992</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3547576186874863</v>
+        <v>-0.3618508917065171</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4640174838569138</v>
+        <v>-0.4711460962992149</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6299520226150648</v>
+        <v>-0.6369837469089958</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.215623345111794</v>
+        <v>-1.222452818920203</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.496725612520024</v>
+        <v>-1.483544603224786</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.929887761448875</v>
+        <v>-1.916689022494111</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.536791190696718</v>
+        <v>-2.543310461176041</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.49814158846641</v>
+        <v>-2.504706729867003</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.114361910738111</v>
+        <v>-3.120697203853382</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.694836552533545</v>
+        <v>-2.701388344183869</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.133418934948843</v>
+        <v>-3.12643564984284</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.008772</t>
+          <t>X &lt; -0.008771</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1466325835737265</v>
+        <v>-0.1511669265916922</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6977735895159256</v>
+        <v>-0.7022716151235997</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8142968172006988</v>
+        <v>-0.8187939517832845</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.568648714341137</v>
+        <v>-0.5732171840734068</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3062210459952794</v>
+        <v>-0.3109248672895859</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4806688152086949</v>
+        <v>-0.4852923477554967</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.9069668897738197</v>
+        <v>-0.9114613189901704</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.356578131217191</v>
+        <v>-1.360969279260082</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.515585204593215</v>
+        <v>-1.502386465638452</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.923322174398223</v>
+        <v>-1.927607450795499</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.914230998291679</v>
+        <v>-1.918539773633036</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.156380159030682</v>
+        <v>-2.160609347584092</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.741146500764025</v>
+        <v>-1.745550927678906</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.062458176586901</v>
+        <v>-2.057955556557495</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2776948799767425</v>
+        <v>-0.2803914021461296</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2992376549590077</v>
+        <v>-0.3020146600413369</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4158666374370981</v>
+        <v>-0.4186320385369484</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2406517265972283</v>
+        <v>-0.2434628338430329</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.004370963916755954</v>
+        <v>-0.007281075140973314</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1872491202862605</v>
+        <v>-0.1900916173556482</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2852937728201468</v>
+        <v>-0.2881136635500283</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6781534652829251</v>
+        <v>-0.6808849473531424</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4602274688131871</v>
+        <v>-0.4630273557181823</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.8851076096090367</v>
+        <v>-0.8878300510275636</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7520865066277409</v>
+        <v>-0.75486023185627</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.9062010632953204</v>
+        <v>-0.908929423135298</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.929926178021546</v>
+        <v>-0.9326714910065022</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.190671820409676</v>
+        <v>-1.188001362660501</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_14.xlsx
@@ -568,833 +568,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.25</t>
+          <t>X ≈ -0.2498</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.69572473846325</v>
+        <v>16.66677143350405</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-15.5849999125943</v>
+        <v>-15.58630455809617</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6395947972073017</v>
+        <v>-0.6397491788791712</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5099783574274994</v>
+        <v>-0.5104710342407017</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.047103420931805</v>
+        <v>-0.9986697044359971</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7503693272897678</v>
+        <v>-0.7264615507673042</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8349347159548799</v>
+        <v>-0.7870097359952055</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.301360467789358</v>
+        <v>-1.25219161451183</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.362450295199203</v>
+        <v>-1.289289732749118</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.472894828350206</v>
+        <v>5.572156729683726</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.416926592036809</v>
+        <v>-2.3170989466606</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.07173960849578</v>
+        <v>-9.948118533756436</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.886578727407276</v>
+        <v>5.035234021834121</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.113479485342282</v>
+        <v>5.285478244908944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.2412</t>
+          <t>X ≈ -0.241</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14.13954781041102</v>
+        <v>14.11057430121708</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.080304221309291</v>
+        <v>-4.081518513177784</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.14630725535748</v>
+        <v>12.14624606822072</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.346686746792869</v>
+        <v>-4.347204855898525</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.74508113753807</v>
+        <v>11.79359065099641</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.58896016573842</v>
+        <v>-4.56507300071776</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.67446802034511</v>
+        <v>-4.626561289153507</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.50025622740372</v>
+        <v>11.54947565956591</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.203868775940073</v>
+        <v>-5.130721433272996</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10.5960313666962</v>
+        <v>10.69530654204893</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.260233933462224</v>
+        <v>-6.160414342756489</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.22745480713256</v>
+        <v>-6.103829040493693</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.01351654700717</v>
+        <v>10.16217510268438</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053130329</v>
+        <v>-6.252983293563666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.2324</t>
+          <t>X ≈ -0.2323</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.587764376092366</v>
+        <v>6.558727523336771</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.515766786791517</v>
+        <v>9.514661365196005</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.19022914223842</v>
+        <v>18.19021376055176</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.79031799229549</v>
+        <v>13.78992107633606</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.884732722486703</v>
+        <v>-4.836323282959341</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.05242701622106694</v>
+        <v>-0.02851616436311843</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.938368943308483</v>
+        <v>8.98633870845871</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.14181886311804</v>
+        <v>-5.092666285310372</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.415687880045219</v>
+        <v>8.48888003498454</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.513266319977255</v>
+        <v>-1.414023955024156</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.823963778286029</v>
+        <v>2.923800964218891</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.402184715940706</v>
+        <v>7.525828238198159</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>16.07260634989039</v>
+        <v>16.22126880664255</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>16.30229067414998</v>
+        <v>16.47428943371457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.2237</t>
+          <t>X ≈ -0.2235</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.13896959564904</v>
+        <v>16.6658653969565</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.84541838006416</v>
+        <v>22.76177084369483</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.14570250838023</v>
+        <v>14.70277456431657</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.27862440066982</v>
+        <v>14.83598106350331</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20.05963255156743</v>
+        <v>22.02698207705732</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>12.04476219246445</v>
+        <v>6.950664091796462</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20.28216389225857</v>
+        <v>14.57092904786556</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.179186295968741</v>
+        <v>-1.252153207155736</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.119143255601948</v>
+        <v>-1.28931528917245</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.5959366102631</v>
+        <v>5.572076681976732</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>18.72120069847178</v>
+        <v>13.05611729630346</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18.76015249036211</v>
+        <v>13.11743326538618</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>18.34473635656506</v>
+        <v>12.72559633778649</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>18.57501794687347</v>
+        <v>12.97778593721663</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.2149</t>
+          <t>X ≈ -0.2147</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.79763629931211</v>
+        <v>0.4283357232502496</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1924494137163464</v>
+        <v>-1.149284202154966</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.050940348423893</v>
+        <v>-4.475800200212987</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.771789302065862</v>
+        <v>-7.281182538868066</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-9.16077165654513</v>
+        <v>-10.70547498327912</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.71745222601964</v>
+        <v>-10.43558783105723</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-14.65701916383974</v>
+        <v>-13.43472105463434</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.42098920035847</v>
+        <v>-8.029309494762998</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-18.04488364141296</v>
+        <v>-16.88069136621421</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-18.8984576093688</v>
+        <v>-17.70790422903018</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.5426957261474</v>
+        <v>-9.09934538768956</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.799587726177364</v>
+        <v>-3.164104766588864</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.348437568282776</v>
+        <v>5.26135981430734</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.575017946878539</v>
+        <v>5.511722588795507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.2061</t>
+          <t>X ≈ -0.2059</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>23</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-13.3082950009593</v>
+        <v>-13.33750381369651</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.91718712814716</v>
+        <v>-14.91849106044747</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.028265057028172</v>
+        <v>2.028132967629013</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.158746291581259</v>
+        <v>2.158273052374305</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.715461808315901</v>
+        <v>-2.667044129264418</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.758163658709535</v>
+        <v>-6.734292379117761</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-15.52468600230472</v>
+        <v>-15.47683675662634</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-20.33596870711114</v>
+        <v>-20.28688362130944</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11.71711752319179</v>
+        <v>-11.64399828720165</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.225702017569951</v>
+        <v>-8.126482783921517</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.08782858704059</v>
+        <v>-3.98800839300177</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2910512344144678</v>
+        <v>0.4146831561150677</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1289599411009519</v>
+        <v>0.0196905380982173</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.444583164266575</v>
+        <v>4.616581923837195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.1973</t>
+          <t>X ≈ -0.1972</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>20</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.457521493757575</v>
+        <v>-7.486678445114897</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9048075281879733</v>
+        <v>0.903634003267463</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.475438912842911</v>
+        <v>-4.475620705455</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.34659683306586</v>
+        <v>-4.347115249056259</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.08153535760646</v>
+        <v>10.13003222914606</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4013975702701416</v>
+        <v>0.4253076827008471</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3171077755649279</v>
+        <v>0.3650322294044912</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1488987148229768</v>
+        <v>-0.09973133367315512</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.203458774326378</v>
+        <v>-5.130318626906835</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.935990522049934</v>
+        <v>4.035242261395396</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>13.72476810244164</v>
+        <v>13.82462476955155</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>8.765021254819082</v>
+        <v>8.888664381685906</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13.34589064007265</v>
+        <v>13.49455016121941</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>18.57501794687952</v>
+        <v>18.74701670644163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.1886</t>
+          <t>X ≈ -0.1885</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8485714718820105</v>
+        <v>-0.8952692962740727</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7568132491842903</v>
+        <v>-2.473194389021018</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.475293508528736</v>
+        <v>-6.083875617884722</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.62809219684496</v>
+        <v>3.697067524664718</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.884412819549333</v>
+        <v>-6.445227909195694</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.588434938534135</v>
+        <v>-6.174178978474806</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.980796446940523</v>
+        <v>0.2040194758852891</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11.49994829531995</v>
+        <v>9.401899804138289</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>21.42933371514734</v>
+        <v>19.0325835388773</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>17.25568777511856</v>
+        <v>14.99178524136855</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.39385211244165</v>
+        <v>8.344801682194657</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>13.76241595409726</v>
+        <v>11.62914763930993</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.34584740120901</v>
+        <v>11.23701554302398</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>16.90835128021057</v>
+        <v>14.71475864192924</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.1798</t>
+          <t>X ≈ -0.1797</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>34</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.405086410429959</v>
+        <v>-5.434175312173899</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.716517684772683</v>
+        <v>7.64756344847325</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.407979968554805</v>
+        <v>-4.475245266331008</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.454389918034749</v>
+        <v>4.453966651679032</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.72205310790343</v>
+        <v>12.77059044249932</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.152257235405756</v>
+        <v>10.11138027827454</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.94139073854005</v>
+        <v>12.98939571211349</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.668613453158422</v>
+        <v>3.717815913665746</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6712772000356324</v>
+        <v>0.7444538741146047</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.698666800650429</v>
+        <v>5.797934841355612</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.556634076163306</v>
+        <v>2.656476144756418</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.531241529864381</v>
+        <v>8.594553205803869</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>8.05303486843593</v>
+        <v>11.1421150013633</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>11.22207677040667</v>
+        <v>14.33525200056021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.171</t>
+          <t>X ≈ -0.1709</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.751225967510443</v>
+        <v>-2.502555442651129</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.801797404394712</v>
+        <v>-4.081115821411544</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.030763791377275</v>
+        <v>6.021369955655757</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.047135806520508</v>
+        <v>3.527343555443203</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.047217647134865</v>
+        <v>0.4149443246648872</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.926200486784559</v>
+        <v>5.940071291645808</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8348972259396348</v>
+        <v>0.6274819709603747</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.379213346674497</v>
+        <v>8.045347939872663</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.320031698280111</v>
+        <v>8.010565661945996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.47254756710155</v>
+        <v>7.189571606531295</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.831519330869682</v>
+        <v>9.616971684302797</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.867830338614574</v>
+        <v>7.047284298103548</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.449832971456416</v>
+        <v>6.65405952506346</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.677582049442513</v>
+        <v>4.273332495918794</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.1623</t>
+          <t>X ≈ -0.1622</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>40</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>12.47567244869149</v>
+        <v>12.44671110166448</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.396789176623031</v>
+        <v>3.395639464654423</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.989101928763404</v>
+        <v>7.989020692737952</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.133891249911805</v>
+        <v>3.133428817001494</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.598045622812087</v>
+        <v>2.646490280094866</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.895901059537721</v>
+        <v>2.919824161925405</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.30768279626097</v>
+        <v>5.355628797487491</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1491673709983914</v>
+        <v>-0.1000040116330112</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.280141371226222</v>
+        <v>7.35332184168454</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.93033626633499</v>
+        <v>9.029597953460652</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.230090313724745</v>
+        <v>6.329927656930323</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.268645748389062</v>
+        <v>1.392274683772278</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.650383138640542</v>
+        <v>-1.501736535248263</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.924982053123898</v>
+        <v>-3.752983293556092</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.1535</t>
+          <t>X ≈ -0.1534</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>58</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.473637763647652</v>
+        <v>-2.502740767227507</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6.232252971330524</v>
+        <v>6.231131522019695</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6823211037118426</v>
+        <v>0.6821810691417056</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.531801315803619</v>
+        <v>2.531335753767216</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>8.875898859847773</v>
+        <v>8.924385381481699</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.45496978080817</v>
+        <v>7.478920875424606</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4888293265855523</v>
+        <v>0.536748125970945</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.698408136771413</v>
+        <v>-1.64925421966857</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.481620825727745</v>
+        <v>-3.408483533505297</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.557577357898388</v>
+        <v>2.656817674944968</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.630991573116674</v>
+        <v>0.7308143645726233</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.057720307371525</v>
+        <v>-0.9340967014740968</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.478006569331157</v>
+        <v>-1.329360975796746</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.976706191054568</v>
+        <v>-2.804707431487131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.1447</t>
+          <t>X ≈ -0.1446</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.704677661351411</v>
+        <v>6.440323779961034</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9.035417756356161</v>
+        <v>7.420137874710818</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>8.643847729771991</v>
+        <v>7.029153958658256</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12.71250710673305</v>
+        <v>13.55327733560657</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>13.49172877176881</v>
+        <v>14.34797333694726</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>13.79265750226909</v>
+        <v>14.62459616310274</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.71222610007329</v>
+        <v>14.5683828835614</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>9.30912082078688</v>
+        <v>10.2677659308194</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>11.87876677049054</v>
+        <v>11.51395086284129</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5179510571245132</v>
+        <v>0.4486727593559365</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.62833987159123</v>
+        <v>1.525896832640719</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.663137383181699</v>
+        <v>1.584442824889287</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.07184488242017295</v>
+        <v>-0.09184500957505293</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.161824158385322</v>
+        <v>-1.12477816535155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.136</t>
+          <t>X ≈ -0.1358</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>71</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-18.67871557915954</v>
+        <v>-18.64193126819329</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-11.90920004330991</v>
+        <v>-10.39818745688572</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-9.503191478653534</v>
+        <v>-7.985627371073051</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.150677546556061</v>
+        <v>-6.454304528530862</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.298328778903759</v>
+        <v>-5.538970770711224</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-12.43536439070593</v>
+        <v>-13.69971226701153</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.716545109078886</v>
+        <v>-10.95211632921622</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.579573641141877</v>
+        <v>-5.795083462677738</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.864014070409958</v>
+        <v>-8.646580348427698</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-11.14916633041026</v>
+        <v>-10.87864536546233</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.138461310117002</v>
+        <v>-6.863724762532456</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.73641368293776</v>
+        <v>-12.43816960793309</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-19.41549685444577</v>
+        <v>-19.87690853988465</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-16.98836233481321</v>
+        <v>-18.22481427947094</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.1272</t>
+          <t>X ≈ -0.1271</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.495434920073983</v>
+        <v>6.675416983872644</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.86905046516533</v>
+        <v>5.099151526406928</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.01661793555967</v>
+        <v>8.642602507455607</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.15488730782896</v>
+        <v>8.773845200537401</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.840364730230753</v>
+        <v>5.663541365772815</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.752433429211067</v>
+        <v>4.625482184353302</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.505209156771805</v>
+        <v>0.6269860019830631</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.417504989921383</v>
+        <v>0.1625746491104465</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.744032061726216</v>
+        <v>1.439714322445674</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1051682601932455</v>
+        <v>-2.01123873856708</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.879046617879858</v>
+        <v>-3.53051820031439</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.619455738925083</v>
+        <v>-8.733536035325656</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.039606592238179</v>
+        <v>-10.44643771391532</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.258315386455457</v>
+        <v>-4.937193819871879</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.1184</t>
+          <t>X ≈ -0.1183</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.642098424756831</v>
+        <v>-4.715563371188431</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.166414745100596</v>
+        <v>-6.29479113349921</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.646855183728206</v>
+        <v>-6.689932952737479</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-11.94299837073645</v>
+        <v>-12.10254195054024</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-10.3133366504825</v>
+        <v>-10.37722509953073</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.677071115294318</v>
+        <v>-5.672798424609638</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-12.27711837659692</v>
+        <v>-11.27874593732166</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.489038805221924</v>
+        <v>-7.309818420767968</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.63901225048783</v>
+        <v>-8.458309063867475</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.49167703848792</v>
+        <v>-9.283388944939794</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-12.78668413282623</v>
+        <v>-11.71038989853708</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-14.92621902394892</v>
+        <v>-13.87651329407762</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-15.34636987726258</v>
+        <v>-13.1648045787771</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-15.12063422703629</v>
+        <v>-12.91964996022276</v>
       </c>
     </row>
     <row r="22">
@@ -1404,631 +1404,631 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.664953705763551</v>
+        <v>6.051643808095498</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.028660983731463</v>
+        <v>0.4498740112398139</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.495315391333563</v>
+        <v>-4.977299095352933</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-10.45859102131219</v>
+        <v>-9.885116466736548</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8130509241658501</v>
+        <v>0.7054809292889388</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5157824724387794</v>
+        <v>0.9786430226829168</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5999827541244045</v>
+        <v>-0.08877505471522085</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.105665887658034</v>
+        <v>-2.570134461498029</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.9116514837666827</v>
+        <v>1.426596848762351</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9578160415621682</v>
+        <v>-0.4044990486173674</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.918728466996789</v>
+        <v>3.428132342639273</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.953106619351878</v>
+        <v>3.487307682512622</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4921394395083212</v>
+        <v>1.073585264535424</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7178750897346191</v>
+        <v>1.322774282201486</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.1009</t>
+          <t>X ≈ -0.1008</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-11.21022420231525</v>
+        <v>-11.46557846805005</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-11.79185010913614</v>
+        <v>-13.08285863232626</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-17.33159651219797</v>
+        <v>-17.68408719186521</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-17.20694552409515</v>
+        <v>-16.5064568318937</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-13.63384195610912</v>
+        <v>-14.90302602400596</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-13.34052591396243</v>
+        <v>-13.58364344891847</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-14.45830229639236</v>
+        <v>-14.70779679896101</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-11.83926448979268</v>
+        <v>-12.50418093439485</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-8.813077800379006</v>
+        <v>-9.390618801922685</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.63478666964091</v>
+        <v>-9.176153449970435</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.811336754968288</v>
+        <v>-8.788302882728487</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.746030767561891</v>
+        <v>-7.680837091594782</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-8.197109455926842</v>
+        <v>-9.1306220331603</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-13.1260129809578</v>
+        <v>-14.14772013566136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.09209</t>
+          <t>X ≈ -0.09203</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.9925829438703246</v>
+        <v>-2.08810594739397</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3627785305225899</v>
+        <v>0.193090716082331</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.968877387310833</v>
+        <v>-5.103840517022661</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.792247261474522</v>
+        <v>-7.906640398179277</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-10.32131271206872</v>
+        <v>-10.35977957267687</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.02719964078543</v>
+        <v>-9.551986035851058</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.10328076980732</v>
+        <v>-10.60400687664353</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.56258586852743</v>
+        <v>-12.06074368654556</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-16.58567686848735</v>
+        <v>-16.44919416031729</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-18.43041312914053</v>
+        <v>-18.68762706250097</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-18.64118262615381</v>
+        <v>-18.89167981650843</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-17.61670546389726</v>
+        <v>-17.85982127917055</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-15.0665592875077</v>
+        <v>-15.32042079675957</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-17.81112066698414</v>
+        <v>-18.01768917590903</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.08332</t>
+          <t>X ≈ -0.08327</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.34692572518157</v>
+        <v>-3.875177967281026</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.954102163933932</v>
+        <v>-5.486819013995024</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.724443785795394</v>
+        <v>-2.356343308840785</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8449871299912033</v>
+        <v>-1.341433674611118</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.258799174843681</v>
+        <v>-1.834234305389735</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.589501932198068</v>
+        <v>-4.213488987582764</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.551123243722841</v>
+        <v>-5.562380842397076</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.772279457180346</v>
+        <v>-6.918038844946118</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.082900399316209</v>
+        <v>-5.186264748278589</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.934732960378859</v>
+        <v>-6.019699038748094</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.142137984847345</v>
+        <v>-6.224618327607274</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.230566850035679</v>
+        <v>-5.659839586718341</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.057100013698637</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-5.810505417449896</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.07455</t>
+          <t>X ≈ -0.0745</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.764310684842194</v>
+        <v>-1.781371212283268</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.928449741248301</v>
+        <v>-1.915421269648498</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.683471094724808</v>
+        <v>5.650695978512772</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.630852339333714</v>
+        <v>3.610562251409753</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.821127433623175</v>
+        <v>3.846679434530841</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.203798945951405</v>
+        <v>1.222935225806886</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.032195618437051</v>
+        <v>4.059239891811195</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.831837902976474</v>
+        <v>2.869768112815223</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.606327498363385</v>
+        <v>-1.512078487473389</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.2764756862935016</v>
+        <v>-0.1626533886743644</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.06056544034741052</v>
+        <v>-0.3667257792073215</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.02618728799208725</v>
+        <v>-0.3085136705068265</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4463381413056595</v>
+        <v>-0.7041107877247441</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.410383512976772</v>
+        <v>-2.629794887759154</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.06578</t>
+          <t>X ≈ -0.06574</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>188</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.532125700893353</v>
+        <v>-3.316245990855528</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.609021031871535</v>
+        <v>-4.376432211896777</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.944263382560969</v>
+        <v>-3.709677193803458</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9610376256274478</v>
+        <v>1.202707127232479</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1075883149081349</v>
+        <v>-0.05916755248589567</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.845691635638048</v>
+        <v>2.871358877390861</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4255268876557992</v>
+        <v>-0.3780780725628361</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.702095600890118</v>
+        <v>0.7512419462299675</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.704421003231758</v>
+        <v>1.777416524770487</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.514224240975373</v>
+        <v>3.612065792198223</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.37335286994923</v>
+        <v>4.471047120712313</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.280071447836463</v>
+        <v>2.403173598993249</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.391835488140188</v>
+        <v>2.540242332701716</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.553741351132565</v>
+        <v>1.725740110699348</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.05702</t>
+          <t>X ≈ -0.05697</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1980241128462197</v>
+        <v>-0.7557973555399684</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.550763272822238</v>
+        <v>-2.851109498380033</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.158695650037068</v>
+        <v>2.809391771463865</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.780169849649894</v>
+        <v>2.437156055213109</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.922035569372206</v>
+        <v>-7.140414605146582</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-6.117976995654558</v>
+        <v>-6.362779476466208</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.637165535846663</v>
+        <v>-2.892916769660559</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.614856074228399</v>
+        <v>-3.867027612905481</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.657735502609604</v>
+        <v>-2.89464384961942</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.978611191069781</v>
+        <v>-2.208894886699753</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.203720512595282</v>
+        <v>-2.918056367747297</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.14893419697465</v>
+        <v>-1.85121895255925</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.058880968655409</v>
+        <v>-1.955110897579779</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.302533073530924</v>
+        <v>0.3126732721004686</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.04825</t>
+          <t>X ≈ -0.0482</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.743366562042596</v>
+        <v>-2.024703784556344</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.442032476927444</v>
+        <v>-2.165943875602281</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.727490442518736</v>
+        <v>-5.443612581816055</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.368358496012831</v>
+        <v>-4.355245416893275</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.464823505229795</v>
+        <v>-3.402398337243561</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.65156923582574</v>
+        <v>-3.610190812427355</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.538565803774382</v>
+        <v>-1.748379680530512</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.936780440570949</v>
+        <v>-4.136093180504673</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.483050138844504</v>
+        <v>-4.653626534187467</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.403239013213131</v>
+        <v>-3.554763650941041</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.124848384033712</v>
+        <v>-3.278308855017684</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.505929168876456</v>
+        <v>-5.622876842555513</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-1.212168581806971</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.767977222204877</v>
+        <v>-4.329906370479279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.03947</t>
+          <t>X ≈ -0.03944</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.292149911516582</v>
+        <v>-2.115605181111178</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.917116877410137</v>
+        <v>-4.136846051781632</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.9757021884549388</v>
+        <v>0.930901001020608</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.840860060348945</v>
+        <v>-2.066261196586083</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.9877850631062728</v>
+        <v>0.8020078648860007</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.429221712147353</v>
+        <v>-1.866383086883395</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.883993383747857</v>
+        <v>-5.290023571948602</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.656048516801583</v>
+        <v>2.222781783799157</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7785355854803129</v>
+        <v>-1.17571756960006</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7859822407554802</v>
+        <v>-1.163218557799581</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.522328968636025</v>
+        <v>-3.888549615144129</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.487950816280602</v>
+        <v>-3.832022735803939</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.220337956513745</v>
+        <v>-2.547419425696219</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.948188804177512</v>
+        <v>-4.992479091875225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.0307</t>
+          <t>X ≈ -0.03068</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.935340742105943</v>
+        <v>4.843141770880045</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.726874814868488</v>
+        <v>5.007970040040263</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.857518766735375</v>
+        <v>1.653323978835481</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.988897328399695</v>
+        <v>2.134085213032499</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.35253622465099</v>
+        <v>2.34659045804549</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.940665585644041</v>
+        <v>1.917621590899628</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.145539272002985</v>
+        <v>1.155211115709207</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.599133841998913</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.016320792418362</v>
+        <v>-2.154611797670498</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.577974340584909</v>
+        <v>-4.031071957432843</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.364235782533044</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.393687417411762</v>
+        <v>-3.475291281639215</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.168448199803265</v>
+        <v>-4.2213264011855</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.588102620498724</v>
+        <v>-3.972281539170133</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.02193</t>
+          <t>X ≈ -0.02191</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.9736986391289832</v>
+        <v>-0.993847479933315</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.428478348044877</v>
+        <v>2.472367655613724</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.641022948523357</v>
+        <v>-1.625074036404641</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.511099778331051</v>
+        <v>-1.8318903318903</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.048558904587424</v>
+        <v>-2.321139472842248</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9214763676055568</v>
+        <v>0.6452487395793227</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.172198107273225</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.706110877023896</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.358444478475711</v>
+        <v>-0.5916133925668632</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.55188264011759</v>
+        <v>-3.43564399358403</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.422135637842594</v>
+        <v>-3.303084104419661</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.725550127627855</v>
+        <v>-4.928419050556457</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.804563857195397</v>
+        <v>-2.966674620217923</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.913276367504025</v>
+        <v>-2.717629758202634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ -0.01316</t>
+          <t>X ≈ -0.01315</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.455011632666029</v>
+        <v>2.547223302973059</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.564000370897496</v>
+        <v>-1.559955576709505</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.294584963123498</v>
+        <v>-3.287026898357539</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.095327734460319</v>
+        <v>-2.090476190476252</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.8378755957016111</v>
+        <v>0.886941335238518</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6008528075174695</v>
+        <v>0.6263935207241502</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.315412792976147</v>
+        <v>1.365737431498694</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4888997548993927</v>
+        <v>-0.4334286622179917</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.476340393026319</v>
+        <v>1.39626539531185</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.495905888489283</v>
+        <v>2.439103481163592</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.29120473022909</v>
+        <v>2.234963033627473</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.731999994883907</v>
+        <v>4.693129770992364</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.113988179003627</v>
+        <v>5.097971844428542</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.607103508374578</v>
+        <v>5.613683373110575</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.004385</t>
+          <t>X ≈ -0.004383</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr"/>
@@ -2182,1509 +2182,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2544</t>
+          <t>X &gt; -0.2542</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2464837961021118</v>
+        <v>-0.245133744029701</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1350918646826997</v>
+        <v>-0.1347018211268818</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2234970118958515</v>
+        <v>-0.2228943447513032</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2999523725849969</v>
+        <v>-0.2991365203161465</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2872625328691001</v>
+        <v>-0.2876401697183724</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2210357708660524</v>
+        <v>-0.2210095516972075</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1457127410108257</v>
+        <v>-0.1464576904525288</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.0612802689691776</v>
+        <v>-0.06228122788440515</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03802337402414935</v>
+        <v>0.03618730844023332</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0582094108861213</v>
+        <v>0.0557009915370088</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1120439816969281</v>
+        <v>0.1093770961274743</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06228329687890977</v>
+        <v>0.05918593704853237</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1457554781349231</v>
+        <v>0.1418409211261462</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1159292648586288</v>
+        <v>0.1115415048802646</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2456</t>
+          <t>X &gt; -0.2454</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4069</v>
+        <v>4080</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3006122578738868</v>
+        <v>-0.2990197164090986</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08573113609512006</v>
+        <v>-0.0854687731904491</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2221676260002852</v>
+        <v>-0.221566130819042</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2992813630487561</v>
+        <v>-0.2984631505413944</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2848349261979735</v>
+        <v>-0.285374634436188</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2193446093439348</v>
+        <v>-0.2193990428766384</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1435107538704301</v>
+        <v>-0.1444167157976111</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05731835140106512</v>
+        <v>-0.0584898467505397</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.04249773079482821</v>
+        <v>0.04041064214990797</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.04091009645333088</v>
+        <v>0.03812404923408508</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1201237598877753</v>
+        <v>0.1171085148912567</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.09466036686414014</v>
+        <v>0.09107195619569808</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1306090779774962</v>
+        <v>0.1262492274229032</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.09996265073568367</v>
+        <v>0.09505592213017877</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2368</t>
+          <t>X &gt; -0.2366</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4063</v>
+        <v>4074</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3219366389739946</v>
+        <v>-0.3202415043584779</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07983218494787536</v>
+        <v>-0.07958357475159517</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2404326639742322</v>
+        <v>-0.2397808763257174</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2933043922630176</v>
+        <v>-0.2925003497971232</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3026000003752856</v>
+        <v>-0.3031639794810133</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2128918174811787</v>
+        <v>-0.2129989339549354</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.1378156192241775</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.07438589938847429</v>
+        <v>-0.07558552496308124</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0502452570169396</v>
+        <v>0.04802644785744548</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.02532291269220366</v>
+        <v>0.02242864055542526</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1295458977563655</v>
+        <v>0.1263537621042943</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1039964955975847</v>
+        <v>0.1001955217283879</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1160145801152836</v>
+        <v>0.1114687769438802</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1095983062176344</v>
+        <v>0.1044050225951096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.228</t>
+          <t>X &gt; -0.2279</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4041</v>
+        <v>4052</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3595544123794454</v>
+        <v>-0.3575902996717275</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1320725159001768</v>
+        <v>-0.1316747368144888</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3407728173364362</v>
+        <v>-0.3398450130511108</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3699784067298069</v>
+        <v>-0.3689596961384254</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2776539672432747</v>
+        <v>-0.2785515647039887</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2137654194677481</v>
+        <v>-0.2140005679458099</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1862268166615948</v>
+        <v>-0.1873544630566215</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.04679779614617985</v>
+        <v>-0.04834569852487647</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.004702139544370709</v>
+        <v>0.00219752907246118</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03369929554760631</v>
+        <v>0.03022774151859409</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1148769560657783</v>
+        <v>0.1111652531095899</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.06426372132202118</v>
+        <v>0.05987866097756012</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.02914375137610392</v>
+        <v>0.02400194558816793</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.02144209931476126</v>
+        <v>0.01552608452880833</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.2193</t>
+          <t>X &gt; -0.2191</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4029</v>
+        <v>4039</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4027369112864605</v>
+        <v>-0.4123823085987368</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1945520122396118</v>
+        <v>-0.205360003599985</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3779626172641102</v>
+        <v>-0.3882614662587827</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4076510882112601</v>
+        <v>-0.4178985993014166</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3382266746708567</v>
+        <v>-0.3503445672647416</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2502762984310607</v>
+        <v>-0.2370608899504276</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2471900056680525</v>
+        <v>-0.2348557469491581</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.0564060883043922</v>
+        <v>-0.04447110144336364</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.004573932283051363</v>
+        <v>0.006354416083389935</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.002240658720467081</v>
+        <v>0.01239064416134283</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0594597595135653</v>
+        <v>0.06950039137115738</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.008579763707608379</v>
+        <v>0.01785137455584618</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.0254075296520142</v>
+        <v>-0.01687964071997783</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.03381799256181495</v>
+        <v>-0.02619448444492889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.2105</t>
+          <t>X &gt; -0.2103</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3994</v>
+        <v>4005</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4220191001625082</v>
+        <v>-0.4195194903922044</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1979433617409683</v>
+        <v>-0.1973466645860285</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3545389265804388</v>
+        <v>-0.3535607628993773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.360644368760866</v>
+        <v>-0.3596335171677723</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2609134362217844</v>
+        <v>-0.2624358446319022</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1497877762814426</v>
+        <v>-0.1504816350196876</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1209145874066593</v>
+        <v>-0.12279696531089</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.02565710872162441</v>
+        <v>0.02331529190816894</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1535159124389125</v>
+        <v>0.1497151043725609</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1678702128975047</v>
+        <v>0.1628251075042897</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1523679823473572</v>
+        <v>0.1473382831284766</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.05071443124540309</v>
+        <v>0.04486423567916376</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.05497302249821701</v>
+        <v>-0.0616886648075976</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06544274415930573</v>
+        <v>-0.07320801265721144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.2017</t>
+          <t>X &gt; -0.2016</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3971</v>
+        <v>3982</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3473818939881639</v>
+        <v>-0.3449053167518201</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1126896204598467</v>
+        <v>-0.1123174528570559</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3683401080518607</v>
+        <v>-0.367317406747226</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3752366591632494</v>
+        <v>-0.3741769252791372</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2466967118304098</v>
+        <v>-0.2485468465036931</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1115121164235049</v>
+        <v>-0.112453597070342</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.03169606750169152</v>
+        <v>-0.0341121548638057</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1435914813643251</v>
+        <v>0.1406268376148461</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2222705256394946</v>
+        <v>0.2178354981460942</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2164857156174236</v>
+        <v>0.2107040832709401</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1769271667079479</v>
+        <v>0.1712240122974933</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0493224024181842</v>
+        <v>0.04272816456666106</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.05454449086187907</v>
+        <v>-0.06215871042960686</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09156477787721684</v>
+        <v>-0.1002962016424789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.193</t>
+          <t>X &gt; -0.1928</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3951</v>
+        <v>3962</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3113902989501014</v>
+        <v>-0.3088539632517637</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1178402008124095</v>
+        <v>-0.1174459306769648</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3475499344006749</v>
+        <v>-0.3465788741944422</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3551335957671284</v>
+        <v>-0.3541217091066073</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2989783219009539</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1141084701906152</v>
+        <v>-0.1151681921221979</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.033461715910029</v>
+        <v>-0.03612701798481055</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1450720695505368</v>
+        <v>0.1418401549863049</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2497356195395994</v>
+        <v>0.2448327425936156</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1976575465137387</v>
+        <v>0.19139798444143</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1083478655905949</v>
+        <v>0.1023022517863623</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.005203451001314363</v>
+        <v>-0.001925728503096025</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1223776223776269</v>
+        <v>-0.1305923745974482</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1860551991617285</v>
+        <v>-0.1954365999669889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.1842</t>
+          <t>X &gt; -0.1841</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3921</v>
+        <v>3931</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3202652933711576</v>
+        <v>-0.3042294719458027</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1129513481087301</v>
+        <v>-0.09886841803167101</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3159681166950321</v>
+        <v>-0.3013343565006181</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4009119109363155</v>
+        <v>-0.3860695255011422</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2638946608630945</v>
+        <v>-0.2524833686531593</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.07987490884139703</v>
+        <v>-0.06738662652134053</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.04887302549570904</v>
+        <v>-0.0380208214215827</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.0581946692003612</v>
+        <v>0.06881500893602066</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.08768819723196941</v>
+        <v>0.096671899376922</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.06714469090084663</v>
+        <v>0.074681626017437</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.02965234725201782</v>
+        <v>0.03730162030769435</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1000544870483751</v>
+        <v>-0.09364876956191637</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2254244856032344</v>
+        <v>-0.2202377181350386</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3168463734492022</v>
+        <v>-0.313018907903583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.1754</t>
+          <t>X &gt; -0.1753</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3887</v>
+        <v>3897</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2757878254061481</v>
+        <v>-0.2594724386977276</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1551952243932533</v>
+        <v>-0.1664534022403288</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2539335391382451</v>
+        <v>-0.264918402963481</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4433817494197214</v>
+        <v>-0.4282971955098986</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3774841190925855</v>
+        <v>-0.3661052597435202</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1431351334115973</v>
+        <v>-0.1561929069327022</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1625002361921943</v>
+        <v>-0.1516806012881986</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.02661395434196834</v>
+        <v>0.03697871672129338</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08258348251745673</v>
+        <v>0.09102022189653525</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0178851715461974</v>
+        <v>0.02474818764908093</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.007548570873581184</v>
+        <v>0.01445021311464956</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1493120287450651</v>
+        <v>-0.1694503777637237</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2978370449130736</v>
+        <v>-0.3193703823544212</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.41777855428046</v>
+        <v>-0.4408200910926539</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.1667</t>
+          <t>X &gt; -0.1665</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3848</v>
+        <v>3859</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2405637901821152</v>
+        <v>-0.2373845521597104</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1283715536499912</v>
+        <v>-0.1279052882396812</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3277649310015747</v>
+        <v>-0.3268201800112962</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4686234814056078</v>
+        <v>-0.4672488276778779</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3706962792813471</v>
+        <v>-0.3737963414246721</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2147838052379214</v>
+        <v>-0.2162234950503503</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1556854018366423</v>
+        <v>-0.1593531013517975</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.03777049895870732</v>
+        <v>-0.0418805811485683</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.01936610195228639</v>
+        <v>0.01303558164728003</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.0373985689492855</v>
+        <v>-0.04580462134743613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.07174843007231857</v>
+        <v>-0.08010687833523633</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.2405143626517656</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.376360727511404</v>
+        <v>-0.3880385182657662</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4998261279668341</v>
+        <v>-0.4872408732399478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.1579</t>
+          <t>X &gt; -0.1578</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3808</v>
+        <v>3819</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.374137700254316</v>
+        <v>-0.3702370858473145</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1654005529175606</v>
+        <v>-0.1648107059185833</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4151269778478479</v>
+        <v>-0.4139198487491811</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5064650227009508</v>
+        <v>-0.5049621311047261</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4018805429587999</v>
+        <v>-0.4054306605817217</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2474590664225289</v>
+        <v>-0.2490702890485181</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2130737232452375</v>
+        <v>-0.2171167242775809</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.03660036374821374</v>
+        <v>-0.04127179947289505</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.05690254583419829</v>
+        <v>-0.06384618069927228</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1315974642779096</v>
+        <v>-0.1408598983812936</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1379442151962422</v>
+        <v>-0.1472452342950774</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2463148815319371</v>
+        <v>-0.2576161070500333</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3629781391592104</v>
+        <v>-0.3763737053096818</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4638475993412428</v>
+        <v>-0.4530356632863857</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.1491</t>
+          <t>X &gt; -0.149</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3750</v>
+        <v>3761</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3416654326071651</v>
+        <v>-0.3373508285965698</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2643509274259372</v>
+        <v>-0.2634452842808415</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4321008415093033</v>
+        <v>-0.4308232928432219</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5534568754031568</v>
+        <v>-0.5517861878243764</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5453768643888779</v>
+        <v>-0.5493097699780733</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3665899659263658</v>
+        <v>-0.3682469674690054</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2239298237492875</v>
+        <v>-0.2287423986499277</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01089773685878015</v>
+        <v>-0.0164744103818677</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.003933569771852774</v>
+        <v>-0.01226708831354273</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1731900348608946</v>
+        <v>-0.1840040885575576</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1498370887221441</v>
+        <v>-0.1607861693480785</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.2337651442789479</v>
+        <v>-0.2471838085983862</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.345732366105878</v>
+        <v>-0.3616772783784796</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.4167695206233617</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.1403</t>
+          <t>X &gt; -0.1402</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3674</v>
+        <v>3683</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4874253877353283</v>
+        <v>-0.4808910456662119</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4567250210479941</v>
+        <v>-0.4261711833851933</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6198450144590524</v>
+        <v>-0.5888135794620339</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8278752920178434</v>
+        <v>-0.8505086843835912</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8357470408581165</v>
+        <v>-0.8648101996115756</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6594867562319848</v>
+        <v>-0.6857712042826307</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5122117644707131</v>
+        <v>-0.5421216470920953</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2036907173653333</v>
+        <v>-0.2342780342248503</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2497379317369948</v>
+        <v>-0.2563737948544187</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.187486911015192</v>
+        <v>-0.197403163805248</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1866202811510647</v>
+        <v>-0.1965073950214702</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2730042820271805</v>
+        <v>-0.2859747066195766</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3513979754581271</v>
+        <v>-0.3673918906420326</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.4097398103356014</v>
+        <v>-0.4017750394154405</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.1316</t>
+          <t>X &gt; -0.1315</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3603</v>
+        <v>3612</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1289514483539449</v>
+        <v>-0.1239049283352571</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2310448304899637</v>
+        <v>-0.2301542522061979</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4447915592945222</v>
+        <v>-0.4434166306236165</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7426910122309351</v>
+        <v>-0.7403565512345267</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7675140951458701</v>
+        <v>-0.7729316280312588</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4274336582448583</v>
+        <v>-0.4299600704360813</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3308330058064968</v>
+        <v>-0.3374955057768076</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1174604404882444</v>
+        <v>-0.1249709507752002</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.07998672278728947</v>
+        <v>-0.09145002262194879</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02852175919769451</v>
+        <v>0.01255480859719427</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.04962868718586577</v>
+        <v>-0.06545190413186219</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.02740282006086403</v>
+        <v>-0.04710265844869355</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.02427535798848623</v>
+        <v>0.01610082311661643</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.08304477862927229</v>
+        <v>-0.05143290595919581</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.1228</t>
+          <t>X &gt; -0.1227</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3531</v>
+        <v>3536</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2640281457560434</v>
+        <v>-0.2700442002039765</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3350399767055308</v>
+        <v>-0.3446981546877055</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6581083204470275</v>
+        <v>-0.6387043722791645</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.964901615188829</v>
+        <v>-0.9448473128676298</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9226450142699392</v>
+        <v>-0.9112721109297652</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5534462411666468</v>
+        <v>-0.5386177659575679</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3682714186373204</v>
+        <v>-0.3582253119390728</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.169150474753188</v>
+        <v>-0.1311512295057753</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1579616172888407</v>
+        <v>-0.1243596635227178</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.02695887387578466</v>
+        <v>0.0560526337059386</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.008065476226754242</v>
+        <v>0.00902350268653862</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1274053957868375</v>
+        <v>0.1395967014615636</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1887045566337235</v>
+        <v>0.2409743889578024</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.03868921823179505</v>
+        <v>0.05357779241676042</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.114</t>
+          <t>X &gt; -0.1139</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3439</v>
+        <v>3446</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.146906172604524</v>
+        <v>-0.1539395207528429</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2057912187257926</v>
+        <v>-0.1892981639468303</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4978975872624218</v>
+        <v>-0.4806629990228544</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6712159793905172</v>
+        <v>-0.6534391534391517</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6714255811406744</v>
+        <v>-0.6640475697300872</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.416379219235921</v>
+        <v>-0.4045271509608597</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.04968638806671777</v>
+        <v>-0.07301148248915013</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.08017483097613365</v>
+        <v>0.0563357255765311</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1224270591445134</v>
+        <v>0.09330007125122819</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3351049930782963</v>
+        <v>0.2999730463809485</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3503501415459951</v>
+        <v>0.3151022044016116</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.530119395965869</v>
+        <v>0.5056587733125539</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6042982896719451</v>
+        <v>0.5910963004772825</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.3647824132919055</v>
+        <v>0.3924026611740317</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.1053</t>
+          <t>X &gt; -0.1052</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3341</v>
+        <v>3347</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3173827568846974</v>
+        <v>-0.3374927772679328</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.18165436240416</v>
+        <v>-0.2082040633622739</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3513106537697581</v>
+        <v>-0.3476582265290702</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3841274567600763</v>
+        <v>-0.3803778884207958</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6672713507855548</v>
+        <v>-0.7045564796204005</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4134634698154258</v>
+        <v>-0.4454395642236975</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.03354480055590159</v>
+        <v>-0.07254521608628295</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1736236158986557</v>
+        <v>0.1340233707872756</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.09927710595296446</v>
+        <v>0.05386284956804843</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.373029644797775</v>
+        <v>0.3208104343118805</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2750130939871269</v>
+        <v>0.2230227351200043</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4590470380215876</v>
+        <v>0.4174653935662747</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.6075881930889011</v>
+        <v>0.5768248910235201</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3544253099421937</v>
+        <v>0.3648834527839142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.09648</t>
+          <t>X &gt; -0.09641</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3244</v>
+        <v>3252</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.008327976841179918</v>
+        <v>-0.012410323201415</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.165506237914272</v>
+        <v>0.1679005442796608</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1564229246111069</v>
+        <v>0.1587872690757592</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1188976210856438</v>
+        <v>0.09070990359332853</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2795533024759393</v>
+        <v>-0.2897795402856431</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.0269267691118884</v>
+        <v>-0.06163594520586457</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3977750135921099</v>
+        <v>0.354991346144061</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5328252639418309</v>
+        <v>0.5032206060247688</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3657686059265188</v>
+        <v>0.3297625288090131</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6423755703528116</v>
+        <v>0.5982432661097974</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5168059223930115</v>
+        <v>0.4862687171912228</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.6744886370171486</v>
+        <v>0.6540394206543141</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8708605950477519</v>
+        <v>0.8604065201125266</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.7575086990350783</v>
+        <v>0.7888371246480901</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.08771</t>
+          <t>X &gt; -0.08765</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3143</v>
+        <v>3150</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.04049215214880775</v>
+        <v>0.05480267796291827</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1591669119348111</v>
+        <v>0.1670848625260533</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.321123952770229</v>
+        <v>0.3291961688160967</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.3496717228888286</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04313766168851174</v>
+        <v>0.03629665123939674</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2944310291824195</v>
+        <v>0.2456706291578854</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7673603251171954</v>
+        <v>0.7098541457390937</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9536450298913692</v>
+        <v>0.9100537354984723</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9105016612608523</v>
+        <v>0.8730811263616758</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.255277784367713</v>
+        <v>1.222738114845775</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.132446025289354</v>
+        <v>1.113745145901504</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.26227438445347</v>
+        <v>1.253535862362931</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.383008036389818</v>
+        <v>1.384357118944571</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.354209801792933</v>
+        <v>1.39781035723756</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.07894</t>
+          <t>X &gt; -0.07888</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3029</v>
+        <v>3037</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1679816331708111</v>
+        <v>0.2010284971636267</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3516108454604066</v>
+        <v>0.3774540222385525</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4357474992200352</v>
+        <v>0.4291191062462048</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4523107920203842</v>
+        <v>0.4125939849624061</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1297737790093052</v>
+        <v>0.1058949383974834</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4782436266064423</v>
+        <v>0.4115860182562372</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.005163932528141</v>
+        <v>0.9432300277474539</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.282055525608172</v>
+        <v>1.201319610240063</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.173706624914125</v>
+        <v>1.098535879023622</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.563518532106613</v>
+        <v>1.49221305668182</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.443869787968652</v>
+        <v>1.386789292265178</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.544276332532625</v>
+        <v>1.510767151709715</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.68536681299274</v>
+        <v>1.661237150550988</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.64698889438467</v>
+        <v>1.66601571862698</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.07017</t>
+          <t>X &gt; -0.07012</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2892</v>
+        <v>2899</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2595183024542749</v>
+        <v>0.2953959203797965</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.4596220143328509</v>
+        <v>0.4866008971196933</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.187152017690245</v>
+        <v>0.1805583582735295</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3017367284028438</v>
+        <v>0.2603623117062028</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.04509325096376671</v>
+        <v>-0.07217621043535161</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4438725758629332</v>
+        <v>0.3729636689488984</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8617672032855666</v>
+        <v>0.794899789306335</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.208639140511536</v>
+        <v>1.121897087523486</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.305402570588065</v>
+        <v>1.222807966838936</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.650682850198173</v>
+        <v>1.570989037868152</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.515137985160663</v>
+        <v>1.470261206671253</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.618672430738677</v>
+        <v>1.597369688262276</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.786350069818077</v>
+        <v>1.773833913394064</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.839194986987899</v>
+        <v>1.870507565360782</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.0614</t>
+          <t>X &gt; -0.06135</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2704</v>
+        <v>2711</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.523138521621938</v>
+        <v>0.5458528290158142</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8120276699121476</v>
+        <v>0.8238381617803654</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4743953961100829</v>
+        <v>0.450334929203251</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2558977606963992</v>
+        <v>0.1950134274129809</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.04074817994988678</v>
+        <v>-0.07307832319614249</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2768821974466107</v>
+        <v>0.1997071956227856</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9512684196675849</v>
+        <v>0.8762424075399764</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.243857404360952</v>
+        <v>1.147600948299278</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.277660164768164</v>
+        <v>1.184347469276737</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.521117102614554</v>
+        <v>1.429446275118593</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.316415944354361</v>
+        <v>1.262165392639638</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.572687587833947</v>
+        <v>1.541489520347326</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.744252710851896</v>
+        <v>1.720685708735324</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.859041615516297</v>
+        <v>1.880546769151394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.05263</t>
+          <t>X &gt; -0.05259</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2508</v>
+        <v>2513</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5794973239966481</v>
+        <v>0.6484102251726114</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.074829513921699</v>
+        <v>1.113388355457957</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2646175453247182</v>
+        <v>0.2644641553203968</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.05862609824229992</v>
+        <v>0.01835435844981959</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.497023880786486</v>
+        <v>0.4837591554453908</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.7766399334305873</v>
+        <v>0.7167674268498487</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.231704247132015</v>
+        <v>1.173215554012607</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.623565475255496</v>
+        <v>1.542704989333323</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.585211022346321</v>
+        <v>1.505732380196527</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.794620589680797</v>
+        <v>1.716112232157997</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.669664248007528</v>
+        <v>1.591526279450861</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.863532033536686</v>
+        <v>1.808802006473677</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.041467304625201</v>
+        <v>2.010302791127032</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.027968505090961</v>
+        <v>2.004079977434756</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.04386</t>
+          <t>X &gt; -0.04382</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8784251051396765</v>
+        <v>0.8896283223629098</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.391209536566535</v>
+        <v>1.409310743336711</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.8036728923406216</v>
+        <v>0.7795530756346594</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4568815571779012</v>
+        <v>0.4130219303679823</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.8534351840917225</v>
+        <v>0.8344406124863042</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.175005556218977</v>
+        <v>1.107226131305232</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.480920196952809</v>
+        <v>1.436856251967036</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.123779123484987</v>
+        <v>2.055151852381613</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.131117176351758</v>
+        <v>2.061544377676732</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.262224647829015</v>
+        <v>2.191748754363907</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.100982855062078</v>
+        <v>2.030973441259732</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.52649529685678</v>
+        <v>2.479426388511882</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.323641271009691</v>
+        <v>2.301094134107643</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.549376921236224</v>
+        <v>2.575650112083828</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.03508</t>
+          <t>X &gt; -0.03506</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.2424882247848</v>
+        <v>1.235659078931285</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.000741203287696</v>
+        <v>2.047910316262765</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.78391952839727</v>
+        <v>0.7621264640033729</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7207210743067094</v>
+        <v>0.6984933305687946</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.8380083811234798</v>
+        <v>0.8381750072269369</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.474037466394762</v>
+        <v>1.44961558168206</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.211775099387907</v>
+        <v>2.211407484715913</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.062660980938468</v>
+        <v>2.035850486306444</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.46521974638771</v>
+        <v>2.434291520130465</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.612236776024034</v>
+        <v>2.578048812561725</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.746682904585548</v>
+        <v>2.712563420661823</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.217107568568771</v>
+        <v>3.206143800987526</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.845406327658459</v>
+        <v>2.859365168086015</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.410289264706698</v>
+        <v>3.447065085737563</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.02631</t>
+          <t>X &gt; -0.02629</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1782</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6580974223804432</v>
+        <v>0.6587047763468874</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.569332853980292</v>
+        <v>1.5745000910795</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6140233526333247</v>
+        <v>0.6195948749309039</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.5200332495849196</v>
+        <v>0.4688953022286313</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5983356247403435</v>
+        <v>0.5969301118939967</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.400193959308169</v>
+        <v>1.374766135763423</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.380506021566667</v>
+        <v>2.380327779422366</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.642136929349427</v>
+        <v>2.644012415223088</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.174419764313257</v>
+        <v>3.168207033920183</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.591832474611977</v>
+        <v>3.635063077123156</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.555481484701957</v>
+        <v>3.599272797937239</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.263260310457952</v>
+        <v>4.274723485919417</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.955342902711322</v>
+        <v>3.99179900492237</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.517778889638187</v>
+        <v>4.633660926421456</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; -0.01754</t>
+          <t>X &gt; -0.01753</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.9870974374791146</v>
+        <v>0.9892152276029265</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.396113364617307</v>
+        <v>1.394926578172651</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.9295469214304219</v>
+        <v>0.9290524290524189</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.131998109075475</v>
+        <v>1.180544028841247</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.496712206050631</v>
+        <v>1.520669615000244</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.624123058905674</v>
+        <v>2.672134737895995</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.032475290539807</v>
+        <v>3.081722852933524</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.886709992630117</v>
+        <v>3.920171119217599</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.03213646605105</v>
+        <v>5.049204491264582</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.962297074479999</v>
+        <v>4.979744178408623</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.075569360348474</v>
+        <v>6.115351993214588</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.318264090312205</v>
+        <v>5.38349372995043</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.016015923950746</v>
+        <v>6.103919063346261</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.008771</t>
+          <t>X &gt; -0.008765</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.492056942438623</v>
+        <v>0.4628611480859917</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.394384362888303</v>
+        <v>2.393197576443647</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.540153518673804</v>
+        <v>2.540000128669483</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.949657941541453</v>
+        <v>1.94916344916345</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.231188208265579</v>
+        <v>1.27973412803135</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.798832508170932</v>
+        <v>1.822789917120545</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.065473500256111</v>
+        <v>3.113485179246432</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.220026478091</v>
+        <v>4.269274040484717</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.699584862108757</v>
+        <v>4.772841971888454</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.887456787068267</v>
+        <v>5.93099537305546</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.863098279845048</v>
+        <v>5.907035105699542</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.528675710829766</v>
+        <v>6.595832473695076</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.387154253368472</v>
+        <v>5.479953826410522</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.153917856705924</v>
+        <v>6.269539228966437</v>
       </c>
     </row>
     <row r="35">
@@ -3848,1509 +3848,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2544</t>
+          <t>X &lt; -0.2542</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.56074553926583</v>
+        <v>14.56059214926151</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19.45287544475895</v>
+        <v>19.45238095238095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.91458589166326</v>
+        <v>18.96313181142903</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.83100754034596</v>
+        <v>16.85496494929558</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.36534480012742</v>
+        <v>14.41335647911774</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.48371886424983</v>
+        <v>4.607415485278075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2456</t>
+          <t>X &lt; -0.2454</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>97</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.49846541276461</v>
+        <v>13.46926961841198</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.794495814546146</v>
+        <v>8.79330902810149</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.52343576999728</v>
+        <v>12.52328237999296</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>16.77737225379185</v>
+        <v>16.77687776141384</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>16.23908270069615</v>
+        <v>16.28762862046192</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>14.47460106022814</v>
+        <v>14.49855846917775</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.32803503085887</v>
+        <v>12.37604670984919</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.737255046865954</v>
+        <v>7.786502609259671</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.583489385188543</v>
+        <v>4.656746494968239</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.764498423910226</v>
+        <v>4.863845749204799</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.467013760495391</v>
+        <v>1.566921796514066</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.532319747902271</v>
+        <v>2.656016368930516</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.081241059537305</v>
+        <v>1.229930607315133</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.306976709763838</v>
+        <v>1.4789754693305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2368</t>
+          <t>X &lt; -0.2366</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>103</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13.53850144519381</v>
+        <v>13.50930565084118</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.0438202064989</v>
+        <v>8.042633420054244</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.50341775378271</v>
+        <v>12.50326436377838</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.54626425659436</v>
+        <v>15.54576976421636</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>15.97884848990643</v>
+        <v>16.0273944096722</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>13.36360116031823</v>
+        <v>13.38755856926784</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.33714322823653</v>
+        <v>11.38515490722685</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.957453225226487</v>
+        <v>8.006700787620204</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.012975923072631</v>
+        <v>4.086233032852327</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.104804699558308</v>
+        <v>5.204152024852881</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.016608395667049</v>
+        <v>1.116516431685724</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.021860334430137</v>
+        <v>2.145556955458382</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.601709481116728</v>
+        <v>1.750399028894556</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8565713449354959</v>
+        <v>1.028570104502158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.228</t>
+          <t>X &lt; -0.2279</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>125</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.31908396946564</v>
+        <v>12.28988817511301</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.307897876401817</v>
+        <v>8.306711089957162</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.51312649164678</v>
+        <v>13.51297310164246</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.24335163523514</v>
+        <v>15.24285714285713</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12.30506208213945</v>
+        <v>12.35360800190522</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11.00243611177454</v>
+        <v>11.02639352072416</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.91772575250837</v>
+        <v>10.9657374314987</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.650657108721624</v>
+        <v>5.699904671115341</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.335054997608793</v>
+        <v>1.434963033627469</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.969433149964118</v>
+        <v>3.093129770992363</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.149282296650711</v>
+        <v>4.297971844428538</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.2193</t>
+          <t>X &lt; -0.2191</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12.48258761910068</v>
+        <v>12.70727947946084</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.411547511438314</v>
+        <v>9.67482703198614</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>13.39633817047889</v>
+        <v>13.62891513062797</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.9864173286658</v>
+        <v>15.20807453416148</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.98827376097156</v>
+        <v>13.26955003089073</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.09586676870885</v>
+        <v>10.64378482507198</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.74108341674194</v>
+        <v>11.30776641700594</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.434598714561048</v>
+        <v>5.044832207347227</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.643689550739005</v>
+        <v>4.283221917051009</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.523697761708412</v>
+        <v>4.184031017395448</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.859142588849679</v>
+        <v>2.530615207540521</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.353374755803543</v>
+        <v>4.03805730722425</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.393077917088675</v>
+        <v>5.09217474297926</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.888886560015933</v>
+        <v>4.61658192383522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.2105</t>
+          <t>X &lt; -0.2103</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>172</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10.30978164388425</v>
+        <v>10.28058584953162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.535804853146004</v>
+        <v>7.534618066701348</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.04801021257702</v>
+        <v>10.0478568225727</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.75963070500259</v>
+        <v>10.75913621262458</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.477155105395262</v>
+        <v>8.525701025161034</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.448947739681508</v>
+        <v>6.472905148631121</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.364237380415339</v>
+        <v>6.41224905940566</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.408796643605349</v>
+        <v>2.458044205999066</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02223309173373167</v>
+        <v>0.09549020151342802</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2462903557589158</v>
+        <v>-0.1469430304643424</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1304038348181038</v>
+        <v>0.2303118708367791</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.490363382522268</v>
+        <v>2.614060003550513</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.977189273394899</v>
+        <v>5.125878821172726</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.621529574784219</v>
+        <v>4.793528334350881</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.2017</t>
+          <t>X &lt; -0.2016</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>195</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.882256850760797</v>
+        <v>4.881070064316141</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.102870081390364</v>
+        <v>9.102716691386043</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.745915737799244</v>
+        <v>9.745421245421241</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.156344133421499</v>
+        <v>7.20489005318727</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.889615598954023</v>
+        <v>4.913573007903636</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.779264214046833</v>
+        <v>3.827275893037154</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2775480194834969</v>
+        <v>-0.2283004570897802</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.290914091867606</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.188448972336133</v>
+        <v>-1.089101647041559</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3675091049553032</v>
+        <v>-0.2676010689366279</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.230971611502589</v>
+        <v>2.354668232530834</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.374923322291743</v>
+        <v>4.52361287006957</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.600658972518275</v>
+        <v>4.772657732084937</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.193</t>
+          <t>X &lt; -0.1928</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>215</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.12373513225635</v>
+        <v>6.094539337903718</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.512549039192521</v>
+        <v>4.511362252747865</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.838707886995621</v>
+        <v>7.8385544969913</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.434049309653744</v>
+        <v>8.433554817275741</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.430643477488289</v>
+        <v>7.479189397254061</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.472203553634998</v>
+        <v>4.496160962584611</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.4572606362293</v>
+        <v>3.505272315219621</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2656219610458095</v>
+        <v>-0.2163743986520927</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.721952954777898</v>
+        <v>-1.648695844998201</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.711406634828684</v>
+        <v>-0.6120593095341107</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9443573231901894</v>
+        <v>1.044265359208865</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.839200591824586</v>
+        <v>2.96289721285283</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.209747412929786</v>
+        <v>5.358436960707614</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.900599342226087</v>
+        <v>6.07259810179275</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.1842</t>
+          <t>X &lt; -0.1841</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.47826764293503</v>
+        <v>5.213465410885377</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.867081549871202</v>
+        <v>3.630288325729524</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.329453022259024</v>
+        <v>6.08207879269937</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.092331227071881</v>
+        <v>7.837979094076651</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.921388612751691</v>
+        <v>5.722713692962131</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.361619785243917</v>
+        <v>3.149970756496508</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.276909425977749</v>
+        <v>3.089314667271047</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.177187720966522</v>
+        <v>0.9974656467251037</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.116205564443746</v>
+        <v>0.9604930375883072</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.490776564032259</v>
+        <v>1.356176651895268</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.102401936384311</v>
+        <v>1.965044334440485</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.177596415270244</v>
+        <v>4.055731397008635</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.206425153793568</v>
+        <v>6.099597860688696</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.248487334632344</v>
+        <v>7.161650852785371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.1754</t>
+          <t>X &lt; -0.1753</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.149908342225508</v>
+        <v>3.918459603684447</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.972414005434082</v>
+        <v>4.120996804242878</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.65291143788334</v>
+        <v>4.798687387356743</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.6505200940165</v>
+        <v>7.428571428571431</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.753807601852714</v>
+        <v>6.58217943047665</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.825375179874889</v>
+        <v>3.997822092152724</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.457510698744926</v>
+        <v>4.294308860070117</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.481481481481488</v>
+        <v>1.328476099686775</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.062076385890606</v>
+        <v>0.9343606334071168</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.004272284901255</v>
+        <v>1.896246338306426</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.157994065709154</v>
+        <v>2.04924874791319</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.342909852473092</v>
+        <v>4.607415485278075</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.431719572636375</v>
+        <v>6.712257558714249</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.732724040067204</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.1667</t>
+          <t>X &lt; -0.1665</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>318</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.179461327956211</v>
+        <v>3.15026553360358</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.140602278917541</v>
+        <v>3.139415492472885</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.947088755797722</v>
+        <v>4.946935365793401</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.96410635221627</v>
+        <v>6.963611859838267</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.796885981510513</v>
+        <v>5.845431901276285</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.207467558315415</v>
+        <v>4.231424967265028</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.808291790244212</v>
+        <v>3.856303469234533</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.083361511237349</v>
+        <v>2.132609073631066</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.707913945909539</v>
+        <v>1.781171055689235</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.430322193604837</v>
+        <v>2.529669518899411</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.854551852954707</v>
+        <v>2.954459888973382</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.775722458140223</v>
+        <v>4.899419079168467</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.556829466462034</v>
+        <v>6.705519014239862</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.725961343103656</v>
+        <v>7.583494693865291</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.1579</t>
+          <t>X &lt; -0.1578</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>358</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.22299458399079</v>
+        <v>4.193798789638159</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.170467708804054</v>
+        <v>3.169280922359398</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.28966280449594</v>
+        <v>5.289509414491619</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.537206383838488</v>
+        <v>6.536711891460484</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.440257612865707</v>
+        <v>5.488803532631479</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.061653988869509</v>
+        <v>4.085611397819122</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.97694362960334</v>
+        <v>4.024955308593661</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.833897332185309</v>
+        <v>1.883144894579026</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.331574393539633</v>
+        <v>2.404831503319329</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.157633250841066</v>
+        <v>3.256980576135639</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.232261701519406</v>
+        <v>3.332169737538081</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.383958289628929</v>
+        <v>4.507654910657173</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.639785089946798</v>
+        <v>5.788474637724626</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.424179958050431</v>
+        <v>6.316849108678547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.1491</t>
+          <t>X &lt; -0.149</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>416</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.288314738696421</v>
+        <v>3.25911894434379</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.600205568709505</v>
+        <v>3.599018782264849</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.647741876262167</v>
+        <v>4.647588486257845</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.979890096773602</v>
+        <v>5.979395604395599</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.922369774447134</v>
+        <v>5.970915694212906</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.537051496389921</v>
+        <v>4.561008905339534</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.490802675585293</v>
+        <v>3.538814354575614</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.34104172410624</v>
+        <v>1.390289286499957</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.520444182968077</v>
+        <v>1.593701292747774</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.074371540484378</v>
+        <v>3.173718865778952</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.869670382224186</v>
+        <v>2.969578418242861</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.625202380733349</v>
+        <v>3.748899001761593</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.64735921972764</v>
+        <v>4.796048767505468</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.113479485338786</v>
+        <v>5.045093629520835</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.1403</t>
+          <t>X &lt; -0.1402</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.819896977595725</v>
+        <v>3.765191818837714</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.444483242255473</v>
+        <v>4.206306231657564</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.269224052622384</v>
+        <v>5.027143142128281</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.025465456373347</v>
+        <v>7.181318681318679</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.096932000838628</v>
+        <v>7.299356989759474</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.971541802831446</v>
+        <v>6.155138459995399</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.07382331348397</v>
+        <v>5.284765771579657</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.574234344493988</v>
+        <v>2.794641513220611</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>3.162527203678948</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.679593554242977</v>
+        <v>2.743556922459113</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.67814442850311</v>
+        <v>2.74184562472059</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.322278678419408</v>
+        <v>3.40729981147819</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.918387987707625</v>
+        <v>4.024287633902226</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.144123637934158</v>
+        <v>4.070903346120026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.1316</t>
+          <t>X &lt; -0.1315</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9704114030939621</v>
+        <v>0.9412156087413308</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.368074867552266</v>
+        <v>2.366888081107611</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.389232686337046</v>
+        <v>3.389079296332724</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.466360484792666</v>
+        <v>5.465865992414663</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.636035533466874</v>
+        <v>5.684581453232646</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.632524607349751</v>
+        <v>3.656482016299364</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.193831947198632</v>
+        <v>3.241843626188952</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.664816400757019</v>
+        <v>1.714063963150736</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.603834244234243</v>
+        <v>1.677091354013939</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9309065983468727</v>
+        <v>1.030253923641446</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.434170041856582</v>
+        <v>1.534078077875257</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.29155704376943</v>
+        <v>1.415253664797675</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9733957718280237</v>
+        <v>1.020095738233849</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.479103204426089</v>
+        <v>1.269140600249216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.1228</t>
+          <t>X &lt; -0.1227</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.594319079183514</v>
+        <v>1.624053541727676</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.647709788627523</v>
+        <v>2.692982540815201</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.133816146819186</v>
+        <v>4.0153131952462</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.988179221442039</v>
+        <v>5.861265879206584</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.763369292170793</v>
+        <v>5.684029218753892</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.866385955034723</v>
+        <v>3.772727374078286</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.997976536207425</v>
+        <v>2.932040083604768</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.747208832859563</v>
+        <v>1.530169881723765</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.842966488249004</v>
+        <v>1.649203512836586</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8363078800069275</v>
+        <v>0.6693686917719859</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.945086345571184</v>
+        <v>0.9332469649847255</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2843468077349272</v>
+        <v>0.2113825011015749</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.04694411844362634</v>
+        <v>-0.3397816657118682</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.055332907507164</v>
+        <v>0.5332881573019463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.114</t>
+          <t>X &lt; -0.1139</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.8067552023423588</v>
+        <v>0.841461362527518</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.661322533936065</v>
+        <v>1.583865672720499</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.773400464249519</v>
+        <v>2.694915646102096</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.725543416057057</v>
+        <v>3.645593120969316</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.735199068440821</v>
+        <v>3.703539602452416</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.662710084377274</v>
+        <v>2.608336065183785</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.071150410042613</v>
+        <v>1.179690919870779</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3301091635161484</v>
+        <v>0.4402603482699305</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2691270069933722</v>
+        <v>0.403287739133134</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7177780907063536</v>
+        <v>-0.5573397472906123</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7854929475966799</v>
+        <v>-0.6246812892179392</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.635230773218318</v>
+        <v>-1.524106891114343</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.980388033019622</v>
+        <v>-1.919264817678169</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9916945703167031</v>
+        <v>-1.123024333227775</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.1053</t>
+          <t>X &lt; -0.1052</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.383818268982552</v>
+        <v>1.465791789570851</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.342680485097475</v>
+        <v>1.448879764655963</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.793319728361752</v>
+        <v>1.778033342606321</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.044317818810015</v>
+        <v>2.028399311531835</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.196849521752974</v>
+        <v>3.346379086242564</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.286494082789027</v>
+        <v>2.414345327953065</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>1.028388033908321</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.07687912316242773</v>
+        <v>0.08062756268161309</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.5255826643881818</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.746234182295261</v>
+        <v>-0.5392097718484834</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.347070606255933</v>
+        <v>-0.1409405808303603</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.091510018113262</v>
+        <v>-0.926147337441364</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.687037315940088</v>
+        <v>-1.562269119426887</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7886184167591139</v>
+        <v>-0.8312965465681401</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.09648</t>
+          <t>X &lt; -0.09641</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.05962451000618074</v>
+        <v>0.1328223714452719</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.0479814666771361</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2166032380829463</v>
+        <v>-0.2259697246790111</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.02173001361352078</v>
+        <v>0.1196640468485128</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.42938640646377</v>
+        <v>1.464287613555705</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.6456793550177764</v>
+        <v>0.7661993459668608</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.736328301545683</v>
+        <v>-0.5889551251356124</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.311505053440527</v>
+        <v>-1.212406344003448</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6157304532065595</v>
+        <v>-0.4934394283022314</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.573757357644524</v>
+        <v>-1.425259369808352</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.129809867256064</v>
+        <v>-1.029901831237389</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-1.620383742521149</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.371194409741484</v>
+        <v>-2.339865993409298</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.086587259196506</v>
+        <v>-2.198929239502036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.08771</t>
+          <t>X &lt; -0.08765</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.04426885704506844</v>
+        <v>-0.08763120473194164</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.001465127863809812</v>
+        <v>-0.02352146818237344</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6857039177099509</v>
+        <v>-0.7079571309156876</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8478764349402965</v>
+        <v>-0.6749723145072082</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2707540899367231</v>
+        <v>0.289266916633899</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4065307498239079</v>
+        <v>-0.2574086131264792</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.758297639304494</v>
+        <v>-1.578976438530411</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.420298056970381</v>
+        <v>-2.284561348302127</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.188882552674443</v>
+        <v>-2.075843448225534</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.233733122883443</v>
+        <v>-3.139884845684684</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.853638959506213</v>
+        <v>-2.805738037453338</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.254957093938316</v>
+        <v>-3.234426217323119</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.623373953349287</v>
+        <v>-3.629584143886945</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.639058299457069</v>
+        <v>-3.7700232156593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.07894</t>
+          <t>X &lt; -0.07888</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3756528726396198</v>
+        <v>-0.4612888083220312</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.495610895528003</v>
+        <v>-0.5623386048989829</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8903822802830419</v>
+        <v>-0.8688926350619823</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8478764349402965</v>
+        <v>-0.7390085938473021</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.01734278389383803</v>
+        <v>0.0795016374762767</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8256340636640616</v>
+        <v>-0.6469049085952321</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.138414598368833</v>
+        <v>-1.970507109986031</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.956360435138023</v>
+        <v>-2.739955468744789</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.578746100432731</v>
+        <v>-2.38116242621043</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.604103493253817</v>
+        <v>-3.421491965421374</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.282488862040324</v>
+        <v>-3.141373513261222</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.552779317112261</v>
+        <v>-3.475291281639215</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.926640374702544</v>
+        <v>-3.870449208203041</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.918385747054153</v>
+        <v>-3.972281539170133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.07017</t>
+          <t>X &lt; -0.07012</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.524734496888037</v>
+        <v>-0.6034970388947585</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6492226243806485</v>
+        <v>-0.7080749022607336</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1832741343313131</v>
+        <v>-0.1679607504976204</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.366038036126362</v>
+        <v>-0.2715397443023946</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4258758536574447</v>
+        <v>0.4843473015161166</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6069535595869695</v>
+        <v>-0.4458806225780378</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.474136532311661</v>
+        <v>-1.321713854549635</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.332441482827669</v>
+        <v>-2.135976764142065</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.471670900696303</v>
+        <v>-2.287731482127619</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.243342435680304</v>
+        <v>-3.070271518836435</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.936832238099896</v>
+        <v>-2.842128444089496</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.174140517747482</v>
+        <v>-3.133474297865227</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.552678487663009</v>
+        <v>-3.528632224429053</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.756222241505803</v>
+        <v>-3.827318191834649</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.0614</t>
+          <t>X &lt; -0.06135</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9120210782833311</v>
+        <v>-0.949731906298112</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.158950691128879</v>
+        <v>-1.1760568883332</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6669553637420336</v>
+        <v>-0.6199984044633737</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1956661000991033</v>
+        <v>-0.08305873231247318</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.357449530979828</v>
+        <v>0.4149793528896097</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1637303275160562</v>
+        <v>-0.02197604449325041</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.339845870956843</v>
+        <v>-1.201223819351071</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.943340162765416</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.936109495277279</v>
+        <v>-1.767428727674279</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.376751347541649</v>
+        <v>-2.214302513386848</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.998733398295641</v>
+        <v>-1.904641601682684</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.473736248942977</v>
+        <v>-2.423377732418274</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.78879015721121</v>
+        <v>-2.750322834971186</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.073408865708252</v>
+        <v>-3.115193389054049</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.05263</t>
+          <t>X &lt; -0.05259</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1658</v>
+        <v>1664</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8272780269264146</v>
+        <v>-0.926130952203188</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.324352424440541</v>
+        <v>-1.373623638076303</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2149120161751199</v>
+        <v>-0.2132671852672914</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1559870142965138</v>
+        <v>0.2154811715481131</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5026394822408164</v>
+        <v>-0.4803632899608061</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8671186415347236</v>
+        <v>-0.7734867904667553</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.493345246288264</v>
+        <v>-1.400729634369583</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.14091930523746</v>
+        <v>-2.014415280951766</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.021396046597779</v>
+        <v>-1.899657866079004</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.329798597440266</v>
+        <v>-2.211646368866425</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.140923328700651</v>
+        <v>-2.023380303707462</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.435386127144312</v>
+        <v>-2.353116475253877</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.702556160251035</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.745850569407438</v>
+        <v>-2.707310216633019</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.04386</t>
+          <t>X &lt; -0.04382</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.038608338226666</v>
+        <v>-1.048123520793418</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.446458082978197</v>
+        <v>-1.461709962674419</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8257297349700039</v>
+        <v>-0.7921837298301568</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3459531775990783</v>
+        <v>-0.2901572112098449</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8307667948659017</v>
+        <v>-0.8038388066054196</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.175103995177338</v>
+        <v>-1.087709725683517</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.498753648240701</v>
+        <v>-1.439374389587577</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.340354127233432</v>
+        <v>-2.249802308106815</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.294327187983065</v>
+        <v>-2.205298215206952</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.448686861787507</v>
+        <v>-2.360896518836434</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.249955709029322</v>
+        <v>-2.162902494654269</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.77582662507605</v>
+        <v>-2.7165872605079</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.524243962727638</v>
+        <v>-2.495617899161203</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.859298407010151</v>
+        <v>-2.887598678171479</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.03508</t>
+          <t>X &lt; -0.03506</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.178215888421605</v>
+        <v>-1.166406025735647</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.722433877152682</v>
+        <v>-1.759484100990505</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6224828018572524</v>
+        <v>-0.5973522166036531</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.51414362093184</v>
+        <v>-0.4892183288409697</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6254882024905299</v>
+        <v>-0.6227015780853407</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.204113484808289</v>
+        <v>-1.174173051513812</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.880754779305505</v>
+        <v>-1.870918213281655</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.778022853291667</v>
+        <v>-1.74470780525516</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.123905294714724</v>
+        <v>-2.087422547950531</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.261573378793884</v>
+        <v>-2.223905033500571</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.393211035645365</v>
+        <v>-2.355287794578864</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.856042135206984</v>
+        <v>-2.839824774462173</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.489994926364027</v>
+        <v>-2.499185900715936</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.094820302409154</v>
+        <v>-3.125021208248036</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.02631</t>
+          <t>X &lt; -0.02629</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4558638384675504</v>
+        <v>-0.4536099553398287</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9592700433976802</v>
+        <v>-0.9566042403294972</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3289127895901629</v>
+        <v>-0.3307509216326849</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.217852378142787</v>
+        <v>-0.1783486783486836</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.273440636388365</v>
+        <v>-0.2706848433526901</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8318735116564255</v>
+        <v>-0.8074808030378122</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.521956122753252</v>
+        <v>-1.511864566836032</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.757383092283405</v>
+        <v>-1.747325649584361</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.111497577114378</v>
+        <v>-2.095401271354788</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.417027763728996</v>
+        <v>-2.438595560103629</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.389787901427646</v>
+        <v>-2.41190936003391</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.919586129164131</v>
+        <v>-2.915380867305508</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.688453552405889</v>
+        <v>-2.704031494469625</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.153169972585836</v>
+        <v>-3.225843418817057</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; -0.01754</t>
+          <t>X &lt; -0.01753</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2683</v>
+        <v>2692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.5135812124200214</v>
+        <v>-0.5130704047686478</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.5830044629966267</v>
+        <v>-0.5799753005753772</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4749864355448992</v>
+        <v>-0.4729684447874405</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3618508917065171</v>
+        <v>-0.3601036269430082</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4711460962992149</v>
+        <v>-0.4961513464842682</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6369837469089958</v>
+        <v>-0.6476805533499288</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.222452818920203</v>
+        <v>-1.244118070539102</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.483544603224786</v>
+        <v>-1.504839583888362</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.916689022494111</v>
+        <v>-1.92980060394656</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.543310461176041</v>
+        <v>-2.548433610824567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.504706729867003</v>
+        <v>-2.510120454313153</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.120697203853382</v>
+        <v>-3.137308239401108</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.701388344183869</v>
+        <v>-2.732997334925336</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.12643564984284</v>
+        <v>-3.169773783897845</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.008771</t>
+          <t>X &lt; -0.008765</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3057</v>
+        <v>3067</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1511669265916922</v>
+        <v>-0.1399819547571184</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.7022716151235997</v>
+        <v>-0.6993298324202257</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8187939517832845</v>
+        <v>-0.8158118236336946</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5732171840734068</v>
+        <v>-0.5709875110265159</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3109248672895859</v>
+        <v>-0.3275363413977743</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4852923477554967</v>
+        <v>-0.4923056662677254</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.9114613189901704</v>
+        <v>-0.9257394715592184</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.360969279260082</v>
+        <v>-1.374094678054846</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.502386465638452</v>
+        <v>-1.523786688021453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.927607450795499</v>
+        <v>-1.939405147947468</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.918539773633036</v>
+        <v>-1.930509279076105</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.160609347584092</v>
+        <v>-2.180509851034351</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.745550927678906</v>
+        <v>-1.775822158179018</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.057955556557495</v>
+        <v>-2.095826462776827</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3418</v>
+        <v>3429</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2803914021461296</v>
+        <v>-0.2730403548114495</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3020146600413369</v>
+        <v>-0.3007867304438818</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4186320385369484</v>
+        <v>-0.417259456497078</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2434628338430329</v>
+        <v>-0.2425746687159887</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.007281075140973314</v>
+        <v>-0.0180034000726792</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1900916173556482</v>
+        <v>-0.1947877420049764</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2881136635500283</v>
+        <v>-0.2978248502242522</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6808849473531424</v>
+        <v>-0.6896149795396767</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4630273557181823</v>
+        <v>-0.4777784796638542</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.8878300510275636</v>
+        <v>-0.9070077917755484</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.75486023185627</v>
+        <v>-0.7745940759296346</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.908929423135298</v>
+        <v>-0.9334514006776971</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.9326714910065022</v>
+        <v>-0.9626695549883735</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.188001362660501</v>
+        <v>-1.222362121202636</v>
       </c>
     </row>
   </sheetData>
